--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -423,19 +423,19 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>86</v>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2438645371039323</v>
+        <v>0.2076560448920286</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4090205387552895</v>
+        <v>-0.426223758705346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.596215871814282</v>
+        <v>0.4871996003291405</v>
       </c>
       <c r="M2" t="n">
-        <v>244400128000</v>
+        <v>251727839232</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.25610937585155</v>
+        <v>0.2761509215274789</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4581985075574582</v>
+        <v>0.4891442076825607</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,32 +639,32 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.000450949944396</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04239508347386</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74674004</v>
+        <v>0.74961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.53572</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4200732766105226</v>
+        <v>0.1329889481707318</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2868987671470742</v>
+        <v>-0.4357850609756097</v>
       </c>
       <c r="L3" t="n">
-        <v>1.464186412467847</v>
+        <v>0.3051709663314389</v>
       </c>
       <c r="M3" t="n">
-        <v>5562502742016</v>
+        <v>42484879360</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.123159403974308</v>
+        <v>0.6242648649930138</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2970472917197908</v>
+        <v>0.4514077307430893</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,109 +713,111 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.4928519097558826</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1.000450949944396</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.04239508347386</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.71474</v>
+        <v>0.74674004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.43910998</v>
+        <v>0.53572</v>
       </c>
       <c r="J4" t="n">
-        <v>0.221314367816092</v>
+        <v>0.4988207430482385</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.961</v>
+        <v>-0.2474689633056942</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2302959082373486</v>
+        <v>2.015690114772307</v>
       </c>
       <c r="M4" t="n">
-        <v>254769070080</v>
+        <v>5271048421376</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1158710591376246</v>
+        <v>0.06669722286781954</v>
       </c>
       <c r="S4" t="n">
-        <v>2.299641483719194</v>
+        <v>0.1946541308810243</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.08087962506974211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.6534957812135467</v>
       </c>
       <c r="H5" t="n">
-        <v>0.74961</v>
+        <v>0.90433</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.061079998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06901039659747732</v>
+        <v>0.2129719047110352</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4618124977280162</v>
+        <v>-0.3400277748103835</v>
       </c>
       <c r="L5" t="n">
-        <v>0.149433800377834</v>
+        <v>0.6263367891925858</v>
       </c>
       <c r="M5" t="n">
-        <v>44539502592</v>
+        <v>33705799680</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -825,62 +827,62 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5937083330349822</v>
+        <v>0.251824158196462</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4071818947670449</v>
+        <v>0.2380054660798332</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H6" t="n">
-        <v>0.38952</v>
+        <v>0.67944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14473</v>
+        <v>0.14088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1977175646291374</v>
+        <v>0.1559331759578719</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3332326648949021</v>
+        <v>-0.2954421645178863</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5933318832698928</v>
+        <v>0.5277959434542107</v>
       </c>
       <c r="M6" t="n">
-        <v>204132728832</v>
+        <v>3680323239936</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -889,7 +891,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -899,33 +901,33 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1945088969397628</v>
+        <v>0.2721294926115181</v>
       </c>
       <c r="S6" t="n">
-        <v>0.259858263710129</v>
+        <v>0.2383381805824003</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72.5</v>
+        <v>74.2</v>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -933,28 +935,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.06713489726936261</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.006929629272242499</v>
-      </c>
+        <v>0.4878747583673768</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3487</v>
+        <v>0.04528</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4884182413755791</v>
+        <v>0.1483026561250778</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8736953934231106</v>
+        <v>-0.4357732966154393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5590257715128519</v>
+        <v>0.3403206604831313</v>
       </c>
       <c r="M7" t="n">
-        <v>1148129771520</v>
+        <v>101209694208</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -963,40 +963,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1767761689947756</v>
+        <v>0.2205355697448483</v>
       </c>
       <c r="S7" t="n">
-        <v>1.746890376291639</v>
+        <v>0.4788491281272171</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -1007,32 +1007,32 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.2027465724146367</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2285599828574523</v>
+        <v>0.1792330812083591</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67944</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14088</v>
+        <v>0.1433</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1465182309385631</v>
+        <v>0.1234997276476542</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3011807084250551</v>
+        <v>-0.2083884522605244</v>
       </c>
       <c r="L8" t="n">
-        <v>0.486479468438538</v>
+        <v>0.5926418969380151</v>
       </c>
       <c r="M8" t="n">
-        <v>3710545297408</v>
+        <v>153607716864</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1047,30 +1047,30 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2015280836479112</v>
+        <v>0.0739651567046733</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2268315631847659</v>
+        <v>0.2830377383397216</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>72</v>
@@ -1081,32 +1081,32 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H9" t="n">
-        <v>0.55724</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05128</v>
+        <v>0.24063</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2853506292271291</v>
+        <v>0.171337866090409</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6875431873861424</v>
+        <v>-0.1838929004374639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.415029389371098</v>
+        <v>0.9317263781408222</v>
       </c>
       <c r="M9" t="n">
-        <v>779621105664</v>
+        <v>498616074240</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1121,26 +1121,26 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02399331515985126</v>
+        <v>0.1719062955910109</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48178571689113</v>
+        <v>0.1484264229690482</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1155,37 +1155,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.3459787421885367</v>
+        <v>0.2230660589034148</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3328887406583814</v>
+        <v>0.2972340671812952</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93036</v>
+        <v>0.38952</v>
       </c>
       <c r="I10" t="n">
-        <v>0.022839999</v>
+        <v>0.14473</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1416374433167782</v>
+        <v>0.1828492612011439</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3635283955949039</v>
+        <v>-0.3008817921830315</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3896186516186515</v>
+        <v>0.6077112871287126</v>
       </c>
       <c r="M10" t="n">
-        <v>157807394816</v>
+        <v>206943928320</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1195,30 +1195,30 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09838686751587034</v>
+        <v>0.1025396709569864</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3912707391772128</v>
+        <v>0.2810940606230861</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>71</v>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6534957812135467</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H11" t="n">
-        <v>0.90433</v>
+        <v>0.77282</v>
       </c>
       <c r="I11" t="n">
-        <v>0.061079998</v>
+        <v>0.05704</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1401341095155011</v>
+        <v>0.1035569998385273</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.37813716279694</v>
+        <v>-0.4093331180364929</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3705906832298132</v>
+        <v>0.2529895463510846</v>
       </c>
       <c r="M11" t="n">
-        <v>35771379712</v>
+        <v>203873566720</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1269,30 +1269,30 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3040443142797304</v>
+        <v>0.488254765770479</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1982347273512726</v>
+        <v>0.2494004299711519</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>70</v>
@@ -1303,32 +1303,32 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2027465724146367</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1792330812083591</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.55724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1433</v>
+        <v>0.05128</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05800675725302962</v>
+        <v>0.1916920155774708</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2528094013955197</v>
+        <v>-0.7096661693759324</v>
       </c>
       <c r="L12" t="n">
-        <v>0.229448576409064</v>
+        <v>0.2701157584361691</v>
       </c>
       <c r="M12" t="n">
-        <v>162739781632</v>
+        <v>842569351168</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1343,105 +1343,107 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1923610114439704</v>
+        <v>0.0566690387634774</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2573665935775524</v>
+        <v>1.610144586552342</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D13" t="n">
         <v>70</v>
       </c>
-      <c r="D13" t="n">
-        <v>66</v>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1878825003317091</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>0.1701360960301399</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.365979383233586</v>
+      </c>
       <c r="H13" t="n">
-        <v>0.70488</v>
+        <v>0.62473</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01746</v>
+        <v>0.103310004</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1717577867130768</v>
+        <v>0.1335661808984705</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5811978635299766</v>
+        <v>-0.348307840539564</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2955237751045485</v>
+        <v>0.3834716459197789</v>
       </c>
       <c r="M13" t="n">
-        <v>271606906880</v>
+        <v>31332263936</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2249954961190344</v>
+        <v>0.1033886880969683</v>
       </c>
       <c r="S13" t="n">
-        <v>1.019145735254052</v>
+        <v>0.2722953732972837</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1449,73 +1451,71 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1382198495222513</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.173598959321368</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.84796</v>
       </c>
       <c r="I14" t="n">
-        <v>0.24063</v>
+        <v>0.17292999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1583345418760034</v>
+        <v>0.1704217544698918</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1980110840627752</v>
+        <v>-0.3639299168809423</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7996246403348145</v>
+        <v>0.4682817942819589</v>
       </c>
       <c r="M14" t="n">
-        <v>507393736704</v>
+        <v>401863442432</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1814388483028617</v>
+        <v>0.2757857292607997</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1126430407173609</v>
+        <v>0.08944622623803955</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1523,37 +1523,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G15" t="n">
-        <v>2.336504917866317</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H15" t="n">
-        <v>0.77282</v>
+        <v>0.97725</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05704</v>
+        <v>0.1911</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0447715156424795</v>
+        <v>0.1320330139020112</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4355591559618872</v>
+        <v>-0.2066675664732083</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1027908954034183</v>
+        <v>0.6388666405433651</v>
       </c>
       <c r="M15" t="n">
-        <v>213346304000</v>
+        <v>691647676416</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1563,33 +1563,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3998657393060088</v>
+        <v>0.1632603895031108</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2891448931981548</v>
+        <v>0.2134015991555402</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1597,70 +1597,68 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1701360960301399</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.365979383233586</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.62473</v>
+        <v>0.52225</v>
       </c>
       <c r="I16" t="n">
-        <v>0.103310004</v>
+        <v>0.029719999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07076222980659841</v>
+        <v>0.2630342163901958</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3844141069397042</v>
+        <v>-0.2904184204010892</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1840781296241492</v>
+        <v>0.905707757885764</v>
       </c>
       <c r="M16" t="n">
-        <v>33170012160</v>
+        <v>87504519168</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2064232883548802</v>
+        <v>0.3063587666231378</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2907489500059546</v>
+        <v>0.2485316658314818</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings PLC</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>66</v>
@@ -1671,26 +1669,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.1820341908356484</v>
+        <v>0.1539697807235301</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.45576</v>
+        <v>0.75795</v>
       </c>
       <c r="I17" t="n">
-        <v>0.29354998</v>
+        <v>0.04513</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3246514694800302</v>
+        <v>0.1237578890683899</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7796015448379804</v>
+        <v>-0.4057081313947226</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4164325630569402</v>
+        <v>0.3050416777276349</v>
       </c>
       <c r="M17" t="n">
-        <v>192484655104</v>
+        <v>44753698816</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1709,30 +1707,30 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.002850367079626048</v>
+        <v>0.4226614470611312</v>
       </c>
       <c r="S17" t="n">
-        <v>1.413175079577211</v>
+        <v>0.3843745176173947</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D18" t="n">
         <v>68</v>
@@ -1743,28 +1741,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1005582390165327</v>
+        <v>0.3459787421885367</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2014836612049711</v>
+        <v>0.3328887406583814</v>
       </c>
       <c r="H18" t="n">
-        <v>0.50469</v>
+        <v>0.93036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22840999</v>
+        <v>0.022839999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2054964082561352</v>
+        <v>0.1572557732297253</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6604583130180399</v>
+        <v>-0.3548210572397943</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3111421329789852</v>
+        <v>0.4431974090067858</v>
       </c>
       <c r="M18" t="n">
-        <v>384968884224</v>
+        <v>155677638656</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1783,33 +1781,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01512373068940587</v>
+        <v>0.02952514034916542</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5445076813061343</v>
+        <v>0.3679819960781479</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>68</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1817,26 +1815,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.4878747583673768</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.1546194776009138</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3167495145145989</v>
+      </c>
       <c r="H19" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.80204004</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04528</v>
+        <v>0.14166</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01036409794447635</v>
+        <v>0.04520407509450886</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4798542297928098</v>
+        <v>-0.5287371051451272</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02159842990016224</v>
+        <v>0.08549442559379541</v>
       </c>
       <c r="M19" t="n">
-        <v>109786939392</v>
+        <v>114510700544</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1845,43 +1845,43 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4806596192907207</v>
+        <v>0.07589969633894245</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5839928189273125</v>
+        <v>0.8491706694621828</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1889,28 +1889,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.1546194776009138</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.3167495145145989</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.80204004</v>
+        <v>0.75185996</v>
       </c>
       <c r="I20" t="n">
-        <v>0.14166</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0384008573805108</v>
+        <v>0.1322917674373609</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5294004734787894</v>
+        <v>-0.5855664119183515</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07253649987913988</v>
+        <v>0.2259210308937717</v>
       </c>
       <c r="M20" t="n">
-        <v>114672107520</v>
+        <v>211688292352</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1919,24 +1917,24 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.08024606855191685</v>
+        <v>0.1958410870652747</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8679335091002895</v>
+        <v>0.8728994110813904</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
@@ -1952,10 +1950,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.8</v>
+        <v>66</v>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1975,20 +1973,20 @@
         <v>0.16832</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002958579881656709</v>
+        <v>0.05161052111632514</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3602366863905325</v>
+        <v>-0.332427759940726</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008212877792378184</v>
+        <v>0.1552533432392277</v>
       </c>
       <c r="M21" t="n">
-        <v>25691938816</v>
+        <v>24621694976</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2003,33 +2001,33 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2380348056296557</v>
+        <v>0.1264954016324626</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3211381777628204</v>
+        <v>0.3198957169608165</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67.5</v>
+        <v>65.5</v>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2037,28 +2035,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1337066930484769</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H22" t="n">
-        <v>0.97725</v>
+        <v>0.57167</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1911</v>
+        <v>0.04658</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1180889700589223</v>
+        <v>0.2283457880434783</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2164395979417175</v>
+        <v>-0.2459239130434783</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5455978073417096</v>
+        <v>0.9285220994475138</v>
       </c>
       <c r="M22" t="n">
-        <v>700273459200</v>
+        <v>15790737408</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2067,7 +2065,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2077,33 +2075,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1613153107304006</v>
+        <v>0.1231581453609647</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1864941770015818</v>
+        <v>0.2527166676960533</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2111,26 +2109,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>0.2237651786474262</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.7345580184539504</v>
+      </c>
       <c r="H23" t="n">
-        <v>0.75185996</v>
+        <v>0.74768996</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0078100003</v>
+        <v>0.04249</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08653214453308311</v>
+        <v>0.08534233758394327</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5979352416705772</v>
+        <v>-0.3870067154606505</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1447182545911161</v>
+        <v>0.2205190095535192</v>
       </c>
       <c r="M23" t="n">
-        <v>218200522752</v>
+        <v>137017729024</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2139,43 +2139,43 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2703049083535807</v>
+        <v>0.2857003921721881</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9869928059355442</v>
+        <v>0.1731432889018076</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>66.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2183,26 +2183,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.3291712528765784</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>0.1465900735417971</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.1008848813150681</v>
+      </c>
       <c r="H24" t="n">
-        <v>0.84796</v>
+        <v>0.7800700699999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.17292999</v>
+        <v>0.084910005</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09952389147020013</v>
+        <v>0.09054857898215452</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3898353697011415</v>
+        <v>-0.4124256444150693</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2552972336668627</v>
+        <v>0.2195512820512817</v>
       </c>
       <c r="M24" t="n">
-        <v>418925182976</v>
+        <v>18113243136</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2215,39 +2217,39 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2862835047681325</v>
+        <v>0.2695654880786942</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1092517037977452</v>
+        <v>0.4550608701426258</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>65.7</v>
+        <v>64.7</v>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2255,30 +2257,32 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>0.1853615538475797</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.1450120266616515</v>
+      </c>
       <c r="H25" t="n">
-        <v>0.52225</v>
+        <v>0.70383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.029719999</v>
+        <v>0.014040001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1988538704954423</v>
+        <v>0.1898381974897929</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3231946346762385</v>
+        <v>-0.5778920308483291</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6152759023819964</v>
+        <v>0.32850115135022</v>
       </c>
       <c r="M25" t="n">
-        <v>91742175232</v>
+        <v>270471692288</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2287,39 +2291,39 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.350318824022277</v>
+        <v>0.1828783863643535</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1817268398244434</v>
+        <v>0.9667499613356869</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>Chipotle Mexican Grill, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>65.5</v>
+        <v>63.8</v>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2327,37 +2331,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.097332408585459</v>
+        <v>0.1136408299076579</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.2116972328310951</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.39361998</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.13075</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1071883180824746</v>
+        <v>0.2115850828729282</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.392751639167087</v>
+        <v>-0.225414364640884</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2729162844737966</v>
+        <v>0.9386495098039215</v>
       </c>
       <c r="M26" t="n">
-        <v>27338686464</v>
+        <v>45808132096</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2367,33 +2371,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1983594200281382</v>
+        <v>0.1584000244140624</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3243320712476749</v>
+        <v>0.1117935883330254</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2401,28 +2405,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.03534983888485344</v>
+        <v>0.7634291720222148</v>
       </c>
       <c r="G27" t="n">
-        <v>0.388859258627138</v>
+        <v>0.4181552919037022</v>
       </c>
       <c r="H27" t="n">
-        <v>0.19893</v>
+        <v>0.108219996</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08554</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07692276872591286</v>
+        <v>0.05673316708229414</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7897126721868203</v>
+        <v>-0.5142144638403989</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09740602048705056</v>
+        <v>0.1103297769156157</v>
       </c>
       <c r="M27" t="n">
-        <v>338669076480</v>
+        <v>26344310784</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2431,7 +2435,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2441,33 +2445,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3311851479129055</v>
+        <v>0.2543008863115785</v>
       </c>
       <c r="S27" t="n">
-        <v>2.595238758114921</v>
+        <v>0.2977345944714418</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2475,71 +2479,73 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>0.06564722266304868</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.4161701082120004</v>
+      </c>
       <c r="H28" t="n">
-        <v>0.75795</v>
+        <v>0.63802</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04513</v>
+        <v>0.09882000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.05778073446039134</v>
+        <v>0.06590527174467242</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.436334848562235</v>
+        <v>-0.2700112164780258</v>
       </c>
       <c r="L28" t="n">
-        <v>0.132422919349175</v>
+        <v>0.2440834592145025</v>
       </c>
       <c r="M28" t="n">
-        <v>47185387520</v>
+        <v>12420340736</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3570141041214594</v>
+        <v>0.3046428373512917</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2962791445258133</v>
+        <v>0.2144891603074206</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Global Payments Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2547,71 +2553,73 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.1948193100306586</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>-0.0495682906305519</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.435693379691408</v>
+      </c>
       <c r="H29" t="n">
-        <v>0.44244</v>
+        <v>0.63959</v>
       </c>
       <c r="I29" t="n">
-        <v>0.05815</v>
+        <v>0.023340002</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3031795564280488</v>
+        <v>0.1712967493487372</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.8360066042178484</v>
+        <v>-0.307282817986182</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3626521069312577</v>
+        <v>0.5574563214154074</v>
       </c>
       <c r="M29" t="n">
-        <v>79048572928</v>
+        <v>23363158016</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.02037263771090236</v>
+        <v>0.3581833609922469</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5780656848186252</v>
+        <v>0.2633905888738934</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2619,37 +2627,37 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.0405993172034298</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5822968332827563</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H30" t="n">
-        <v>0.57167</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.04658</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1899473511023364</v>
+        <v>0.1292930282690705</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2694965449160909</v>
+        <v>-0.3806280926951154</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7048229548229551</v>
+        <v>0.3396833569313937</v>
       </c>
       <c r="M30" t="n">
-        <v>16310325248</v>
+        <v>26803562496</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2659,33 +2667,33 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1148202176994255</v>
+        <v>0.1635171558191761</v>
       </c>
       <c r="S30" t="n">
-        <v>0.239520454510977</v>
+        <v>0.269498707302106</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60.9</v>
+        <v>62.8</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2693,28 +2701,26 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.1465900735417971</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-0.1008848813150681</v>
-      </c>
+        <v>0.1948193100306586</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.7800700699999999</v>
+        <v>0.44244</v>
       </c>
       <c r="I31" t="n">
-        <v>0.084910005</v>
+        <v>0.05815</v>
       </c>
       <c r="J31" t="n">
-        <v>0.07667210440456773</v>
+        <v>0.2398508138895181</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4199021207177813</v>
+        <v>-0.8441042900445509</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1825951825951827</v>
+        <v>0.2841483175933854</v>
       </c>
       <c r="M31" t="n">
-        <v>18346690560</v>
+        <v>83154591744</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2727,20 +2733,20 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1714275925138224</v>
+        <v>0.04208680550719479</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3688674871134887</v>
+        <v>0.5046989707469345</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-06 11:35:57</t>
+          <t>2026-09-13 12:39:07</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -418,18 +418,18 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -577,16 +577,16 @@
         <v>0.14119</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2076560448920286</v>
+        <v>0.2088673955564473</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.426223758705346</v>
+        <v>-0.4256482270926325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4871996003291405</v>
+        <v>0.4907042535642751</v>
       </c>
       <c r="M2" t="n">
-        <v>251727839232</v>
+        <v>251475591168</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2761509215274789</v>
+        <v>0.1751635618638367</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4891442076825607</v>
+        <v>0.4633054999840425</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,32 +639,32 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1402968452680178</v>
+        <v>1.000450949944396</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2194365698361114</v>
+        <v>2.04239508347386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74961</v>
+        <v>0.74674004</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.53572</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1329889481707318</v>
+        <v>0.4743330184010437</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4357850609756097</v>
+        <v>-0.2609438970621316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3051709663314389</v>
+        <v>1.817758620689655</v>
       </c>
       <c r="M3" t="n">
-        <v>42484879360</v>
+        <v>5367153557504</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -679,30 +679,30 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6242648649930138</v>
+        <v>0.05614272900761552</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4514077307430893</v>
+        <v>0.2476369802853362</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.5</v>
+        <v>78.2</v>
       </c>
       <c r="D4" t="n">
         <v>78</v>
@@ -713,32 +713,32 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.000450949944396</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04239508347386</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H4" t="n">
-        <v>0.74674004</v>
+        <v>0.67944</v>
       </c>
       <c r="I4" t="n">
-        <v>0.53572</v>
+        <v>0.14088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4988207430482385</v>
+        <v>0.1602640042124024</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2474689633056942</v>
+        <v>-0.2928024626351816</v>
       </c>
       <c r="L4" t="n">
-        <v>2.015690114772307</v>
+        <v>0.5473451376400613</v>
       </c>
       <c r="M4" t="n">
-        <v>5271048421376</v>
+        <v>3666585845760</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -753,33 +753,33 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06669722286781954</v>
+        <v>0.3039261028789282</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1946541308810243</v>
+        <v>0.2744358696236919</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H5" t="n">
-        <v>0.90433</v>
+        <v>0.74961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.061079998</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2129719047110352</v>
+        <v>0.1425244994427577</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3400277748103835</v>
+        <v>-0.4310364705430229</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6263367891925858</v>
+        <v>0.3306553138373751</v>
       </c>
       <c r="M5" t="n">
-        <v>33705799680</v>
+        <v>42130300928</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -827,33 +827,33 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.251824158196462</v>
+        <v>0.6973906475867773</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2380054660798332</v>
+        <v>0.4020690586217381</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2285599828574523</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H6" t="n">
-        <v>0.67944</v>
+        <v>0.77282</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14088</v>
+        <v>0.05704</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1559331759578719</v>
+        <v>0.1873461667787493</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2954421645178863</v>
+        <v>-0.3850033624747814</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5277959434542107</v>
+        <v>0.4866091703056772</v>
       </c>
       <c r="M6" t="n">
-        <v>3680323239936</v>
+        <v>195808165888</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -901,33 +901,33 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2721294926115181</v>
+        <v>0.5702896948865437</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2383381805824003</v>
+        <v>0.2285312880510173</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -935,26 +935,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.4878747583673768</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>0.3168737488062043</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5171329563234539</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.83399004</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04528</v>
+        <v>0.20357001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1483026561250778</v>
+        <v>0.1495802000121429</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4357732966154393</v>
+        <v>-0.3823996253024903</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3403206604831313</v>
+        <v>0.391161994193431</v>
       </c>
       <c r="M7" t="n">
-        <v>101209694208</v>
+        <v>1027672309760</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -963,40 +965,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2205355697448483</v>
+        <v>0.05098654030380989</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4788491281272171</v>
+        <v>0.2605663724727669</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -1007,28 +1009,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2027465724146367</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1792330812083591</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1433</v>
+        <v>0.24063</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1234997276476542</v>
+        <v>0.1795233882952374</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2083884522605244</v>
+        <v>-0.1781897954851037</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5926418969380151</v>
+        <v>1.007484114376489</v>
       </c>
       <c r="M8" t="n">
-        <v>153607716864</v>
+        <v>495155838976</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1047,33 +1049,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0739651567046733</v>
+        <v>0.1559801230513438</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2830377383397216</v>
+        <v>0.1547837233574285</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1081,28 +1083,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.1989383144293926</v>
       </c>
       <c r="G9" t="n">
-        <v>0.173598959321368</v>
+        <v>0.398395285030712</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.81747</v>
       </c>
       <c r="I9" t="n">
-        <v>0.24063</v>
+        <v>0.14591</v>
       </c>
       <c r="J9" t="n">
-        <v>0.171337866090409</v>
+        <v>0.1344809613218176</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1838929004374639</v>
+        <v>-0.2185354862936538</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9317263781408222</v>
+        <v>0.6153735651934846</v>
       </c>
       <c r="M9" t="n">
-        <v>498616074240</v>
+        <v>1696002211840</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1121,33 +1123,33 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1719062955910109</v>
+        <v>0.1533731225359971</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1484264229690482</v>
+        <v>0.09834679777975341</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>71.3</v>
+        <v>70</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1155,37 +1157,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H10" t="n">
-        <v>0.38952</v>
+        <v>0.97725</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14473</v>
+        <v>0.1911</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1828492612011439</v>
+        <v>0.1386723234407667</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3008817921830315</v>
+        <v>-0.2020147166634989</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6077112871287126</v>
+        <v>0.6864466397849459</v>
       </c>
       <c r="M10" t="n">
-        <v>206943928320</v>
+        <v>691411156992</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1195,33 +1197,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1025396709569864</v>
+        <v>0.1275339816928081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2810940606230861</v>
+        <v>0.2336563213589786</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1229,28 +1231,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.1483959547833886</v>
       </c>
       <c r="G11" t="n">
-        <v>2.336504917866317</v>
+        <v>0.6156160063417289</v>
       </c>
       <c r="H11" t="n">
-        <v>0.77282</v>
+        <v>0.55659</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05704</v>
+        <v>0.16832</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1035569998385273</v>
+        <v>0.01938496528609046</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4093331180364929</v>
+        <v>-0.3528848455829543</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2529895463510846</v>
+        <v>0.05493283582089542</v>
       </c>
       <c r="M11" t="n">
-        <v>203873566720</v>
+        <v>25400053760</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1259,7 +1261,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1269,33 +1271,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.488254765770479</v>
+        <v>0.2758093667400658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2494004299711519</v>
+        <v>0.3481441815255868</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1303,37 +1305,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.08087962506974211</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.6534957812135467</v>
       </c>
       <c r="H12" t="n">
-        <v>0.55724</v>
+        <v>0.90433</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05128</v>
+        <v>0.061079998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1916920155774708</v>
+        <v>0.2129348129586539</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7096661693759324</v>
+        <v>-0.336531233219975</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2701157584361691</v>
+        <v>0.6327341772151894</v>
       </c>
       <c r="M12" t="n">
-        <v>842569351168</v>
+        <v>33527404544</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1343,33 +1345,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0566690387634774</v>
+        <v>0.161281495291818</v>
       </c>
       <c r="S12" t="n">
-        <v>1.610144586552342</v>
+        <v>0.1709898188547487</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>70.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1377,32 +1379,32 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1701360960301399</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G13" t="n">
-        <v>0.365979383233586</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H13" t="n">
-        <v>0.62473</v>
+        <v>0.80204004</v>
       </c>
       <c r="I13" t="n">
-        <v>0.103310004</v>
+        <v>0.14166</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1335661808984705</v>
+        <v>-0.03250447479981167</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.348307840539564</v>
+        <v>-0.5669453603391428</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3834716459197789</v>
+        <v>-0.05733264098037193</v>
       </c>
       <c r="M13" t="n">
-        <v>31332263936</v>
+        <v>124613926912</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1417,14 +1419,14 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1033886880969683</v>
+        <v>0.173495483670312</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2722953732972837</v>
+        <v>1.04331076426576</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
@@ -1440,10 +1442,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1461,16 +1463,16 @@
         <v>0.17292999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1704217544698918</v>
+        <v>0.108087930646251</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3639299168809423</v>
+        <v>-0.401204683629813</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4682817942819589</v>
+        <v>0.2694084467517894</v>
       </c>
       <c r="M14" t="n">
-        <v>401863442432</v>
+        <v>426879287296</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1489,33 +1491,33 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2757857292607997</v>
+        <v>0.3827352510449069</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08944622623803955</v>
+        <v>0.1410586314684703</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.8</v>
+        <v>67.7</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1523,32 +1525,32 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1337066930484769</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H15" t="n">
-        <v>0.97725</v>
+        <v>0.62473</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1911</v>
+        <v>0.103310004</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1320330139020112</v>
+        <v>0.05741466144376051</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2066675664732083</v>
+        <v>-0.3944040290990487</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6388666405433651</v>
+        <v>0.1455732122587969</v>
       </c>
       <c r="M15" t="n">
-        <v>691647676416</v>
+        <v>33717184512</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1563,33 +1565,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1632603895031108</v>
+        <v>0.2329239267157031</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2134015991555402</v>
+        <v>0.3282295664174155</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69.8</v>
+        <v>67.3</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1597,30 +1599,32 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>0.1465900735417971</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.1008848813150681</v>
+      </c>
       <c r="H16" t="n">
-        <v>0.52225</v>
+        <v>0.7800700699999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.029719999</v>
+        <v>0.084910005</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2630342163901958</v>
+        <v>0.1375387797311272</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2904184204010892</v>
+        <v>-0.3871078938297139</v>
       </c>
       <c r="L16" t="n">
-        <v>0.905707757885764</v>
+        <v>0.3552983081032947</v>
       </c>
       <c r="M16" t="n">
-        <v>87504519168</v>
+        <v>17365008384</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1629,39 +1633,39 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3063587666231378</v>
+        <v>0.2050408175861098</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2485316658314818</v>
+        <v>0.424807371874228</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1669,26 +1673,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>0.097332408585459</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.06564477917470324</v>
+      </c>
       <c r="H17" t="n">
-        <v>0.75795</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04513</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1237578890683899</v>
+        <v>0.1589903459372486</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4057081313947226</v>
+        <v>-0.3643403057119871</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3050416777276349</v>
+        <v>0.4363786916919681</v>
       </c>
       <c r="M17" t="n">
-        <v>44753698816</v>
+        <v>26116763648</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1697,43 +1703,43 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4226614470611312</v>
+        <v>0.1519926180834859</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3843745176173947</v>
+        <v>0.3986919014560613</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1741,28 +1747,26 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.3459787421885367</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.3328887406583814</v>
-      </c>
+        <v>0.1539697807235301</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.93036</v>
+        <v>0.75795</v>
       </c>
       <c r="I18" t="n">
-        <v>0.022839999</v>
+        <v>0.04513</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1572557732297253</v>
+        <v>0.07640088719244842</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3548210572397943</v>
+        <v>-0.4307525661525765</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4431974090067858</v>
+        <v>0.1773660639444375</v>
       </c>
       <c r="M18" t="n">
-        <v>155677638656</v>
+        <v>46722670592</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1771,43 +1775,43 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.02952514034916542</v>
+        <v>0.6580004670418704</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3679819960781479</v>
+        <v>0.4535161794867335</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.40000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,28 +1819,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H19" t="n">
-        <v>0.80204004</v>
+        <v>0.74768996</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14166</v>
+        <v>0.04249</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04520407509450886</v>
+        <v>0.06499756403631785</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5287371051451272</v>
+        <v>-0.4003100317413449</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08549442559379541</v>
+        <v>0.1623680619583253</v>
       </c>
       <c r="M19" t="n">
-        <v>114510700544</v>
+        <v>140057280512</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1855,33 +1859,33 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.07589969633894245</v>
+        <v>0.4253998307629483</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8491706694621828</v>
+        <v>0.1959919240360959</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1889,26 +1893,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.2900686653697968</v>
+        <v>0.2391183028460648</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.75185996</v>
+        <v>0.68041</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0078100003</v>
+        <v>0.15755</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1322917674373609</v>
+        <v>0.1002811765659184</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5855664119183515</v>
+        <v>-0.3837614455878778</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2259210308937717</v>
+        <v>0.2613112331081078</v>
       </c>
       <c r="M20" t="n">
-        <v>211688292352</v>
+        <v>130036170752</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1927,30 +1931,30 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1958410870652747</v>
+        <v>0.191510745336724</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8728994110813904</v>
+        <v>0.2495529970940369</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="D21" t="n">
         <v>66</v>
@@ -1961,28 +1965,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1483959547833886</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6156160063417289</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H21" t="n">
-        <v>0.55659</v>
+        <v>0.57167</v>
       </c>
       <c r="I21" t="n">
-        <v>0.16832</v>
+        <v>0.04658</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05161052111632514</v>
+        <v>0.2143216924110141</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.332427759940726</v>
+        <v>-0.2545332437877771</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1552533432392277</v>
+        <v>0.8420184696569918</v>
       </c>
       <c r="M21" t="n">
-        <v>24621694976</v>
+        <v>15963761664</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1991,7 +1995,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2001,33 +2005,33 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1264954016324626</v>
+        <v>0.1819700347188102</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3198957169608165</v>
+        <v>0.2486503069103758</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.5</v>
+        <v>64.2</v>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2035,73 +2039,71 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.0405993172034298</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5822968332827563</v>
-      </c>
+        <v>0.2694953937625746</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.57167</v>
+        <v>0.79536</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04658</v>
+        <v>0.0018000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2283457880434783</v>
+        <v>0.2407737473903968</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2459239130434783</v>
+        <v>-0.5737212943632568</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9285220994475138</v>
+        <v>0.4196702297020699</v>
       </c>
       <c r="M22" t="n">
-        <v>15790737408</v>
+        <v>82558525440</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1231581453609647</v>
+        <v>0.03103138192352151</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2527166676960533</v>
+        <v>0.7694319982225872</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2109,28 +2111,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H23" t="n">
-        <v>0.74768996</v>
+        <v>0.55724</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04249</v>
+        <v>0.05128</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08534233758394327</v>
+        <v>0.1012611196456004</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3870067154606505</v>
+        <v>-0.7235182737308421</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2205190095535192</v>
+        <v>0.1399565475014813</v>
       </c>
       <c r="M23" t="n">
-        <v>137017729024</v>
+        <v>913892179968</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2149,33 +2151,33 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2857003921721881</v>
+        <v>0.04177756929308174</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1731432889018076</v>
+        <v>1.727237276134866</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2183,28 +2185,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.1465900735417971</v>
+        <v>0.7634291720222148</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1008848813150681</v>
+        <v>0.4181552919037022</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7800700699999999</v>
+        <v>0.108219996</v>
       </c>
       <c r="I24" t="n">
-        <v>0.084910005</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09054857898215452</v>
+        <v>0.08403683806600148</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4124256444150693</v>
+        <v>-0.5016628293681249</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2195512820512817</v>
+        <v>0.1675165731769504</v>
       </c>
       <c r="M24" t="n">
-        <v>18113243136</v>
+        <v>25286266880</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2213,7 +2215,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2223,33 +2225,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2695654880786942</v>
+        <v>0.2749510876428567</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4550608701426258</v>
+        <v>0.2695680087776442</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2257,28 +2259,26 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1853615538475797</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.1450120266616515</v>
-      </c>
+        <v>0.4878747583673768</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.70383</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.014040001</v>
+        <v>0.04528</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1898381974897929</v>
+        <v>0.07944016024036049</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5778920308483291</v>
+        <v>-0.4699132031380404</v>
       </c>
       <c r="L25" t="n">
-        <v>0.32850115135022</v>
+        <v>0.1690528372258235</v>
       </c>
       <c r="M25" t="n">
-        <v>270471692288</v>
+        <v>107728044032</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2291,39 +2291,39 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1828783863643535</v>
+        <v>0.1079056680933363</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9667499613356869</v>
+        <v>0.6156957089801756</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill, Inc.</t>
+          <t>Global Payments Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63.8</v>
+        <v>62.5</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.1136408299076579</v>
+        <v>-0.0495682906305519</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2116972328310951</v>
+        <v>1.435693379691408</v>
       </c>
       <c r="H26" t="n">
-        <v>0.39361998</v>
+        <v>0.63959</v>
       </c>
       <c r="I26" t="n">
-        <v>0.13075</v>
+        <v>0.023340002</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2115850828729282</v>
+        <v>0.215774629673172</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.225414364640884</v>
+        <v>-0.2809781330825301</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9386495098039215</v>
+        <v>0.7679410041841005</v>
       </c>
       <c r="M26" t="n">
-        <v>45808132096</v>
+        <v>22508439552</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2371,33 +2371,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1584000244140624</v>
+        <v>0.2754310377372089</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1117935883330254</v>
+        <v>0.2559101024364061</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.1</v>
+        <v>61.9</v>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2405,37 +2405,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.7634291720222148</v>
+        <v>0.06564722266304868</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4181552919037022</v>
+        <v>0.4161701082120004</v>
       </c>
       <c r="H27" t="n">
-        <v>0.108219996</v>
+        <v>0.63802</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07877000000000001</v>
+        <v>0.09882000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.05673316708229414</v>
+        <v>0.07928893905191869</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.5142144638403989</v>
+        <v>-0.2654422327108557</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1103297769156157</v>
+        <v>0.2987050637804406</v>
       </c>
       <c r="M27" t="n">
-        <v>26344310784</v>
+        <v>12343085056</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2445,33 +2445,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2543008863115785</v>
+        <v>0.2650570862704869</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2977345944714418</v>
+        <v>0.1649533208018907</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.1</v>
+        <v>61.5</v>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2479,37 +2479,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.06564722266304868</v>
+        <v>0.09890131082105791</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4161701082120004</v>
+        <v>0.1098987103332316</v>
       </c>
       <c r="H28" t="n">
-        <v>0.63802</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09882000000000001</v>
+        <v>0.058530003</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06590527174467242</v>
+        <v>0.1724039982895016</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2700112164780258</v>
+        <v>-0.181633525764379</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2440834592145025</v>
+        <v>0.9491859917598571</v>
       </c>
       <c r="M28" t="n">
-        <v>12420340736</v>
+        <v>52286742528</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2519,33 +2519,33 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3046428373512917</v>
+        <v>0.1412478754855584</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2144891603074206</v>
+        <v>0.09183791056323831</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Global Payments Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.9</v>
+        <v>60.9</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-0.0495682906305519</v>
+        <v>0.05150438997980311</v>
       </c>
       <c r="G29" t="n">
-        <v>1.435693379691408</v>
+        <v>0.1218387563505456</v>
       </c>
       <c r="H29" t="n">
-        <v>0.63959</v>
+        <v>0.88465</v>
       </c>
       <c r="I29" t="n">
-        <v>0.023340002</v>
+        <v>0.45124</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1712967493487372</v>
+        <v>0.07020321984692512</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.307282817986182</v>
+        <v>-0.310965954077593</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5574563214154074</v>
+        <v>0.225758540207935</v>
       </c>
       <c r="M29" t="n">
-        <v>23363158016</v>
+        <v>27402047488</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2593,33 +2593,33 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3581833609922469</v>
+        <v>0.148767420950964</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2633905888738934</v>
+        <v>0.2719320924978099</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.8</v>
+        <v>60.9</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2627,70 +2627,68 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.097332408585459</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.06564477917470324</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.52225</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.029719999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1292930282690705</v>
+        <v>0.3215772779102311</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3806280926951154</v>
+        <v>-0.257282056597906</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3396833569313937</v>
+        <v>1.249901692183723</v>
       </c>
       <c r="M30" t="n">
-        <v>26803562496</v>
+        <v>83600506880</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1635171558191761</v>
+        <v>0.1123025191603533</v>
       </c>
       <c r="S30" t="n">
-        <v>0.269498707302106</v>
+        <v>0.2114781432641872</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.8</v>
+        <v>60.4</v>
       </c>
       <c r="D31" t="n">
         <v>60</v>
@@ -2701,26 +2699,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.1948193100306586</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>-0.02271104500520582</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.02405904398946013</v>
+      </c>
       <c r="H31" t="n">
-        <v>0.44244</v>
+        <v>0.49581</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05815</v>
+        <v>0.07315000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2398508138895181</v>
+        <v>0.1870082508726885</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.8441042900445509</v>
+        <v>-0.4257565704064853</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2841483175933854</v>
+        <v>0.4392374983060036</v>
       </c>
       <c r="M31" t="n">
-        <v>83154591744</v>
+        <v>16511163392</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2729,24 +2729,24 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.04208680550719479</v>
+        <v>0.4688957164107639</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5046989707469345</v>
+        <v>0.6811193597095746</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-13 12:39:07</t>
+          <t>2026-09-20 12:07:31</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -418,16 +418,16 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -545,19 +545,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.8</v>
+        <v>87.8</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -565,32 +565,32 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2714652572159764</v>
+        <v>1.000450949944396</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3708447402164197</v>
+        <v>2.04239508347386</v>
       </c>
       <c r="H2" t="n">
-        <v>0.63004</v>
+        <v>0.74674004</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14119</v>
+        <v>0.53572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2088673955564473</v>
+        <v>0.4559914693206557</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4256482270926325</v>
+        <v>-0.2701381792331274</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4907042535642751</v>
+        <v>1.687993421052632</v>
       </c>
       <c r="M2" t="n">
-        <v>251475591168</v>
+        <v>5434765213696</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1751635618638367</v>
+        <v>0.1703207582185422</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4633054999840425</v>
+        <v>0.3173584005132899</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,32 +639,32 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.000450949944396</v>
+        <v>0.2714652572159764</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04239508347386</v>
+        <v>0.3708447402164197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74674004</v>
+        <v>0.63004</v>
       </c>
       <c r="I3" t="n">
-        <v>0.53572</v>
+        <v>0.14119</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4743330184010437</v>
+        <v>0.1712850157346888</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2609438970621316</v>
+        <v>-0.4455579762769306</v>
       </c>
       <c r="L3" t="n">
-        <v>1.817758620689655</v>
+        <v>0.3844281212648046</v>
       </c>
       <c r="M3" t="n">
-        <v>5367153557504</v>
+        <v>260505960448</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -679,14 +679,14 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05614272900761552</v>
+        <v>0.310596415307818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2476369802853362</v>
+        <v>0.6854344994550787</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
@@ -725,16 +725,16 @@
         <v>0.14088</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1602640042124024</v>
+        <v>0.1183550961892401</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2928024626351816</v>
+        <v>-0.3234786988782765</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5473451376400613</v>
+        <v>0.3658821944061812</v>
       </c>
       <c r="M4" t="n">
-        <v>3666585845760</v>
+        <v>3832843862016</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -753,33 +753,33 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3039261028789282</v>
+        <v>0.3865503487022235</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2744358696236919</v>
+        <v>0.4161317125742567</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -787,28 +787,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2194365698361114</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.74961</v>
+        <v>0.77282</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.05704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1425244994427577</v>
+        <v>0.2010866592598923</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4310364705430229</v>
+        <v>-0.3747542945047433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3306553138373751</v>
+        <v>0.5365826681870011</v>
       </c>
       <c r="M5" t="n">
-        <v>42130300928</v>
+        <v>192598458368</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -827,33 +827,33 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6973906475867773</v>
+        <v>0.4802785214795628</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4020690586217381</v>
+        <v>0.2692554728432814</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.1989383144293926</v>
       </c>
       <c r="G6" t="n">
-        <v>2.336504917866317</v>
+        <v>0.398395285030712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.77282</v>
+        <v>0.81747</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05704</v>
+        <v>0.14591</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1873461667787493</v>
+        <v>0.05136471276907129</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3850033624747814</v>
+        <v>-0.3078519543410584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4866091703056772</v>
+        <v>0.1668487467588597</v>
       </c>
       <c r="M6" t="n">
-        <v>195808165888</v>
+        <v>1914858373120</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -901,62 +901,62 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5702896948865437</v>
+        <v>0.3671116063642994</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2285312880510173</v>
+        <v>0.3751515266561853</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Everpure, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3168737488062043</v>
+        <v>0.0998020993811779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5171329563234539</v>
+        <v>0.3372469555379434</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83399004</v>
+        <v>0.69734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.20357001</v>
+        <v>0.03031</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1495802000121429</v>
+        <v>0.1533</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3823996253024903</v>
+        <v>-0.5493650793650793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.391161994193431</v>
+        <v>0.27904940768564</v>
       </c>
       <c r="M7" t="n">
-        <v>1027672309760</v>
+        <v>41986633728</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -975,30 +975,30 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05098654030380989</v>
+        <v>0.8218622517082297</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2605663724727669</v>
+        <v>1.03094774565783</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -1009,32 +1009,32 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G8" t="n">
-        <v>0.173598959321368</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.74961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24063</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1795233882952374</v>
+        <v>0.05920015676214896</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1781897954851037</v>
+        <v>-0.4725309961522017</v>
       </c>
       <c r="L8" t="n">
-        <v>1.007484114376489</v>
+        <v>0.1252831184498226</v>
       </c>
       <c r="M8" t="n">
-        <v>495155838976</v>
+        <v>45444575232</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1049,30 +1049,30 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1559801230513438</v>
+        <v>0.6379551334970399</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1547837233574285</v>
+        <v>0.5743773535877754</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>71</v>
@@ -1083,28 +1083,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1989383144293926</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G9" t="n">
-        <v>0.398395285030712</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H9" t="n">
-        <v>0.81747</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14591</v>
+        <v>0.24063</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1344809613218176</v>
+        <v>0.1745156346340175</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2185354862936538</v>
+        <v>-0.181678851404915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6153735651934846</v>
+        <v>0.9605720934742562</v>
       </c>
       <c r="M9" t="n">
-        <v>1696002211840</v>
+        <v>497267048448</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1123,33 +1123,33 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1533731225359971</v>
+        <v>0.1394364870224072</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09834679777975341</v>
+        <v>0.1374513063739387</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1157,32 +1157,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1337066930484769</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H10" t="n">
-        <v>0.97725</v>
+        <v>0.62473</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1911</v>
+        <v>0.103310004</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1386723234407667</v>
+        <v>0.09074116832140389</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2020147166634989</v>
+        <v>-0.3753174786423459</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6864466397849459</v>
+        <v>0.2417717625346049</v>
       </c>
       <c r="M10" t="n">
-        <v>691411156992</v>
+        <v>32686991360</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1197,33 +1197,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1275339816928081</v>
+        <v>0.2349587040253922</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2336563213589786</v>
+        <v>0.310637124319542</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1231,28 +1231,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1483959547833886</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6156160063417289</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H11" t="n">
-        <v>0.55659</v>
+        <v>0.74768996</v>
       </c>
       <c r="I11" t="n">
-        <v>0.16832</v>
+        <v>0.04249</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01938496528609046</v>
+        <v>0.0691093496534434</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3528848455829543</v>
+        <v>-0.4009733077717151</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05493283582089542</v>
+        <v>0.1723539904376608</v>
       </c>
       <c r="M11" t="n">
-        <v>25400053760</v>
+        <v>140212355072</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1271,33 +1271,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2758093667400658</v>
+        <v>0.3790929445553863</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3481441815255868</v>
+        <v>0.3085680810099776</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1305,73 +1305,71 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.08087962506974211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.6534957812135467</v>
-      </c>
+        <v>0.2391183028460648</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.90433</v>
+        <v>0.68041</v>
       </c>
       <c r="I12" t="n">
-        <v>0.061079998</v>
+        <v>0.15755</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2129348129586539</v>
+        <v>0.1248888248373548</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.336531233219975</v>
+        <v>-0.3737132504323479</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6327341772151894</v>
+        <v>0.3341835610401054</v>
       </c>
       <c r="M12" t="n">
-        <v>33527404544</v>
+        <v>127949856768</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.161281495291818</v>
+        <v>0.2658147985287158</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1709898188547487</v>
+        <v>0.2275251745239564</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.5</v>
+        <v>69.7</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1379,28 +1377,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1546194776009138</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.3167495145145989</v>
-      </c>
+        <v>0.4878747583673768</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.80204004</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14166</v>
+        <v>0.04528</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.03250447479981167</v>
+        <v>0.08944095477386926</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5669453603391428</v>
+        <v>-0.4680485762144054</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.05733264098037193</v>
+        <v>0.1910933166323698</v>
       </c>
       <c r="M13" t="n">
-        <v>124613926912</v>
+        <v>107350425600</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1409,24 +1405,24 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.173495483670312</v>
+        <v>0.2098490077226263</v>
       </c>
       <c r="S13" t="n">
-        <v>1.04331076426576</v>
+        <v>0.6972282034917359</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
@@ -1442,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1463,16 +1459,16 @@
         <v>0.17292999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.108087930646251</v>
+        <v>0.0310823008382981</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.401204683629813</v>
+        <v>-0.4391838456266146</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2694084467517894</v>
+        <v>0.07077286914765908</v>
       </c>
       <c r="M14" t="n">
-        <v>426879287296</v>
+        <v>455788101632</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1491,33 +1487,33 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3827352510449069</v>
+        <v>0.6795359749968264</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1410586314684703</v>
+        <v>0.2853754493566614</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1525,28 +1521,26 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1701360960301399</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.365979383233586</v>
-      </c>
+        <v>0.1539697807235301</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.62473</v>
+        <v>0.75795</v>
       </c>
       <c r="I15" t="n">
-        <v>0.103310004</v>
+        <v>0.04513</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05741466144376051</v>
+        <v>0.1015140670361574</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3944040290990487</v>
+        <v>-0.4174716283979941</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1455732122587969</v>
+        <v>0.2431639903906944</v>
       </c>
       <c r="M15" t="n">
-        <v>33717184512</v>
+        <v>45657448448</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1555,43 +1549,43 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2329239267157031</v>
+        <v>0.5252395003996511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3282295664174155</v>
+        <v>0.4804250616635359</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.3</v>
+        <v>68.7</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1599,37 +1593,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1465900735417971</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1008848813150681</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7800700699999999</v>
+        <v>0.97725</v>
       </c>
       <c r="I16" t="n">
-        <v>0.084910005</v>
+        <v>0.1911</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1375387797311272</v>
+        <v>0.1414928139800751</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3871078938297139</v>
+        <v>-0.2000381076814198</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3552983081032947</v>
+        <v>0.7073292965029251</v>
       </c>
       <c r="M16" t="n">
-        <v>17365008384</v>
+        <v>689702764544</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1639,14 +1633,14 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2050408175861098</v>
+        <v>0.09467475906268485</v>
       </c>
       <c r="S16" t="n">
-        <v>0.424807371874228</v>
+        <v>0.2071664423134003</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
@@ -1662,10 +1656,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68.2</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1685,16 +1679,16 @@
         <v>0.06315999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1589903459372486</v>
+        <v>0.1579714149355704</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3643403057119871</v>
+        <v>-0.3648991484765517</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4363786916919681</v>
+        <v>0.4329180147311898</v>
       </c>
       <c r="M17" t="n">
-        <v>26116763648</v>
+        <v>26139742208</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1713,33 +1707,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1519926180834859</v>
+        <v>0.197395248425726</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3986919014560613</v>
+        <v>0.3577640494988241</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1747,71 +1741,73 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>0.2230660589034148</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2972340671812952</v>
+      </c>
       <c r="H18" t="n">
-        <v>0.75795</v>
+        <v>0.38952</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04513</v>
+        <v>0.14473</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07640088719244842</v>
+        <v>0.181934712807706</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4307525661525765</v>
+        <v>-0.298311333095493</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1773660639444375</v>
+        <v>0.6098820011959337</v>
       </c>
       <c r="M18" t="n">
-        <v>46722670592</v>
+        <v>207363145728</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6580004670418704</v>
+        <v>0.02883485370679817</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4535161794867335</v>
+        <v>0.3700557048270037</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Seagate Technology Holdings PLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>65.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1819,28 +1815,26 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.2237651786474262</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.7345580184539504</v>
-      </c>
+        <v>0.1820341908356484</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.74768996</v>
+        <v>0.45576</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04249</v>
+        <v>0.29354998</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06499756403631785</v>
+        <v>0.2270540885442229</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4003100317413449</v>
+        <v>-0.7720406182171177</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1623680619583253</v>
+        <v>0.2940960400096067</v>
       </c>
       <c r="M19" t="n">
-        <v>140057280512</v>
+        <v>208480731136</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1849,43 +1843,43 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4253998307629483</v>
+        <v>0.01962985315181021</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1959919240360959</v>
+        <v>1.424085151046378</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>65.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1893,71 +1887,73 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.2391183028460648</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>0.1251174560921597</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3333790189024399</v>
+      </c>
       <c r="H20" t="n">
-        <v>0.68041</v>
+        <v>0.60897</v>
       </c>
       <c r="I20" t="n">
-        <v>0.15755</v>
+        <v>0.12958999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1002811765659184</v>
+        <v>0.2487077518027447</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3837614455878778</v>
+        <v>-0.3142591300302396</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2613112331081078</v>
+        <v>0.7914097890451514</v>
       </c>
       <c r="M20" t="n">
-        <v>130036170752</v>
+        <v>4206119354368</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.191510745336724</v>
+        <v>0.02000969543903452</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2495529970940369</v>
+        <v>0.2257818382032553</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.5</v>
+        <v>67.2</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1965,37 +1961,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.0405993172034298</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5822968332827563</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H21" t="n">
-        <v>0.57167</v>
+        <v>0.80204004</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04658</v>
+        <v>0.14166</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2143216924110141</v>
+        <v>-0.05269549175602461</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2545332437877771</v>
+        <v>-0.5759829355471002</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8420184696569918</v>
+        <v>-0.091487939145231</v>
       </c>
       <c r="M21" t="n">
-        <v>15963761664</v>
+        <v>127269978112</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2005,33 +2001,33 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1819700347188102</v>
+        <v>0.1460852310453788</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2486503069103758</v>
+        <v>1.140688748944991</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64.2</v>
+        <v>67.2</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2039,26 +2035,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.2694953937625746</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>0.1586149467868072</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1210385188280461</v>
+      </c>
       <c r="H22" t="n">
-        <v>0.79536</v>
+        <v>0.5519500000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0018000001</v>
+        <v>0.13573</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2407737473903968</v>
+        <v>0.3454436424533613</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5737212943632568</v>
+        <v>-0.3906964159042877</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4196702297020699</v>
+        <v>0.884174075807206</v>
       </c>
       <c r="M22" t="n">
-        <v>82558525440</v>
+        <v>67199614976</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2067,43 +2065,43 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.03103138192352151</v>
+        <v>0.04278970867203258</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7694319982225872</v>
+        <v>0.2966838562556793</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2111,32 +2109,32 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.1251174560921597</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.3333790189024399</v>
       </c>
       <c r="H23" t="n">
-        <v>0.55724</v>
+        <v>0.60897</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05128</v>
+        <v>0.12958999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1012611196456004</v>
+        <v>0.2382314999413628</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7235182737308421</v>
+        <v>-0.3060718892928345</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1399565475014813</v>
+        <v>0.7783514536136793</v>
       </c>
       <c r="M23" t="n">
-        <v>913892179968</v>
+        <v>4171386060800</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2151,33 +2149,33 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.04177756929308174</v>
+        <v>0.01975381950029775</v>
       </c>
       <c r="S23" t="n">
-        <v>1.727237276134866</v>
+        <v>0.2164523786460073</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.2</v>
+        <v>64.8</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2185,28 +2183,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.7634291720222148</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4181552919037022</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H24" t="n">
-        <v>0.108219996</v>
+        <v>0.55724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.07877000000000001</v>
+        <v>0.05128</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08403683806600148</v>
+        <v>-0.01922204779347625</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5016628293681249</v>
+        <v>-0.747347890205033</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1675165731769504</v>
+        <v>-0.02572034797368964</v>
       </c>
       <c r="M24" t="n">
-        <v>25286266880</v>
+        <v>1029487722496</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2215,7 +2213,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2225,33 +2223,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2749510876428567</v>
+        <v>0.2090762380073785</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2695680087776442</v>
+        <v>2.094812738186907</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>62.8</v>
+        <v>64.2</v>
       </c>
       <c r="D25" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2259,71 +2257,73 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.4878747583673768</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>0.1483959547833886</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6156160063417289</v>
+      </c>
       <c r="H25" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.55659</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04528</v>
+        <v>0.16832</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07944016024036049</v>
+        <v>0.03106893211720085</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4699132031380404</v>
+        <v>-0.3339252562757286</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1690528372258235</v>
+        <v>0.09304157602127176</v>
       </c>
       <c r="M25" t="n">
-        <v>107728044032</v>
+        <v>25112223744</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1079056680933363</v>
+        <v>0.08914285177712911</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6156957089801756</v>
+        <v>0.342835427282056</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Global Payments Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-0.0495682906305519</v>
+        <v>0.7634291720222148</v>
       </c>
       <c r="G26" t="n">
-        <v>1.435693379691408</v>
+        <v>0.4181552919037022</v>
       </c>
       <c r="H26" t="n">
-        <v>0.63959</v>
+        <v>0.108219996</v>
       </c>
       <c r="I26" t="n">
-        <v>0.023340002</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.215774629673172</v>
+        <v>-0.02045769764216365</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2809781330825301</v>
+        <v>-0.5496994914470643</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7679410041841005</v>
+        <v>-0.03721614802354918</v>
       </c>
       <c r="M26" t="n">
-        <v>22508439552</v>
+        <v>28420321280</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2371,33 +2371,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2754310377372089</v>
+        <v>0.4123408262101467</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2559101024364061</v>
+        <v>0.947771278918103</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2405,37 +2405,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.06564722266304868</v>
+        <v>0.09890131082105791</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4161701082120004</v>
+        <v>0.1098987103332316</v>
       </c>
       <c r="H27" t="n">
-        <v>0.63802</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09882000000000001</v>
+        <v>0.058530003</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07928893905191869</v>
+        <v>0.172278674505612</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2654422327108557</v>
+        <v>-0.1817210048102619</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2987050637804406</v>
+        <v>0.9480394117647059</v>
       </c>
       <c r="M27" t="n">
-        <v>12343085056</v>
+        <v>52292333568</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2445,33 +2445,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2650570862704869</v>
+        <v>0.1948353213984786</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1649533208018907</v>
+        <v>0.124408396071563</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>61.5</v>
+        <v>63.4</v>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2479,54 +2479,52 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.09890131082105791</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1098987103332316</v>
-      </c>
+        <v>0.1948193100306586</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.44244</v>
       </c>
       <c r="I28" t="n">
-        <v>0.058530003</v>
+        <v>0.05815</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1724039982895016</v>
+        <v>0.220600753995646</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.181633525764379</v>
+        <v>-0.8430308501035416</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9491859917598571</v>
+        <v>0.2616757784944071</v>
       </c>
       <c r="M28" t="n">
-        <v>52286742528</v>
+        <v>84466008064</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1412478754855584</v>
+        <v>0.1525986522629132</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09183791056323831</v>
+        <v>0.3670877484061343</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
@@ -2542,10 +2540,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.9</v>
+        <v>62.7</v>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2565,16 +2563,16 @@
         <v>0.45124</v>
       </c>
       <c r="J29" t="n">
-        <v>0.07020321984692512</v>
+        <v>0.1293298520452566</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.310965954077593</v>
+        <v>-0.2728981723237598</v>
       </c>
       <c r="L29" t="n">
-        <v>0.225758540207935</v>
+        <v>0.4739124888378614</v>
       </c>
       <c r="M29" t="n">
-        <v>27402047488</v>
+        <v>25967400960</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2593,33 +2591,33 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.148767420950964</v>
+        <v>0.127037152405824</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2719320924978099</v>
+        <v>0.1517527763041562</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.9</v>
+        <v>62.5</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2627,26 +2625,28 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.06564722266304868</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.4161701082120004</v>
+      </c>
       <c r="H30" t="n">
-        <v>0.52225</v>
+        <v>0.63802</v>
       </c>
       <c r="I30" t="n">
-        <v>0.029719999</v>
+        <v>0.09882000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3215772779102311</v>
+        <v>0.09892938027589038</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.257282056597906</v>
+        <v>-0.2630224418365246</v>
       </c>
       <c r="L30" t="n">
-        <v>1.249901692183723</v>
+        <v>0.376125244618395</v>
       </c>
       <c r="M30" t="n">
-        <v>83600506880</v>
+        <v>12302558208</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2655,43 +2655,43 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1123025191603533</v>
+        <v>0.1489059241095896</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2114781432641872</v>
+        <v>0.1885476006334648</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60.4</v>
+        <v>62.4</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2699,28 +2699,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-0.02271104500520582</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.02405904398946013</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H31" t="n">
-        <v>0.49581</v>
+        <v>0.60081</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07315000000000001</v>
+        <v>0.12174</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1870082508726885</v>
+        <v>0.02672196913034619</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4257565704064853</v>
+        <v>-0.3653702318623785</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4392374983060036</v>
+        <v>0.07313668930864453</v>
       </c>
       <c r="M31" t="n">
-        <v>16511163392</v>
+        <v>56725651456</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2739,14 +2739,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.4688957164107639</v>
+        <v>0.2699627827822078</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6811193597095746</v>
+        <v>0.2563517364617405</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-20 12:07:31</t>
+          <t>2026-09-27 12:53:19</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -418,15 +418,15 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87.8</v>
+        <v>89.2</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -577,16 +577,16 @@
         <v>0.53572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4559914693206557</v>
+        <v>0.4007266509938021</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2701381792331274</v>
+        <v>-0.2978414191066466</v>
       </c>
       <c r="L2" t="n">
-        <v>1.687993421052632</v>
+        <v>1.345436280137773</v>
       </c>
       <c r="M2" t="n">
-        <v>5434765213696</v>
+        <v>5649190617088</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1703207582185422</v>
+        <v>0.1977078628548592</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3173584005132899</v>
+        <v>0.3218599940218567</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
         <v>0.14119</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1712850157346888</v>
+        <v>0.1681082228116713</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4455579762769306</v>
+        <v>-0.4476971304557511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3844281212648046</v>
+        <v>0.3754954217386625</v>
       </c>
       <c r="M3" t="n">
-        <v>260505960448</v>
+        <v>261514952704</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.310596415307818</v>
+        <v>0.1966182338656004</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6854344994550787</v>
+        <v>0.6368014335649153</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,37 +713,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1612397915820203</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2285599828574523</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67944</v>
+        <v>0.77282</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14088</v>
+        <v>0.05704</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1183550961892401</v>
+        <v>0.207383143721505</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3234786988782765</v>
+        <v>-0.3765392645617623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3658821944061812</v>
+        <v>0.5507610048659048</v>
       </c>
       <c r="M4" t="n">
-        <v>3832843862016</v>
+        <v>193149878272</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -753,30 +753,30 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3865503487022235</v>
+        <v>0.4192749211426474</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4161317125742567</v>
+        <v>0.262416822895835</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="D5" t="n">
         <v>77</v>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G5" t="n">
-        <v>2.336504917866317</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H5" t="n">
-        <v>0.77282</v>
+        <v>0.67944</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05704</v>
+        <v>0.14088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2010866592598923</v>
+        <v>0.1184326512472706</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3747542945047433</v>
+        <v>-0.325256506869167</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5365826681870011</v>
+        <v>0.3641207746688053</v>
       </c>
       <c r="M5" t="n">
-        <v>192598458368</v>
+        <v>3842942959616</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -827,14 +827,14 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4802785214795628</v>
+        <v>0.3407051562809811</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2692554728432814</v>
+        <v>0.3913867942988862</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>77</v>
@@ -873,16 +873,16 @@
         <v>0.14591</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05136471276907129</v>
+        <v>0.09185899901109762</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3078519543410584</v>
+        <v>-0.2854356664102846</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1668487467588597</v>
+        <v>0.3218203252814933</v>
       </c>
       <c r="M6" t="n">
-        <v>1914858373120</v>
+        <v>1854788337664</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -901,62 +901,62 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3671116063642994</v>
+        <v>0.2138377464221191</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3751515266561853</v>
+        <v>0.2695921368463412</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Everpure, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.0998020993811779</v>
+        <v>0.06713489726936261</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3372469555379434</v>
+        <v>-0.006929629272242499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.69734</v>
+        <v>0.80716</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03031</v>
+        <v>0.44557</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1533</v>
+        <v>0.4141183749034785</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5493650793650793</v>
+        <v>-0.8329038320200206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.27904940768564</v>
+        <v>0.4971983066750067</v>
       </c>
       <c r="M7" t="n">
-        <v>41986633728</v>
+        <v>1213973397504</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -975,33 +975,33 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8218622517082297</v>
+        <v>0.09153593769833712</v>
       </c>
       <c r="S7" t="n">
-        <v>1.03094774565783</v>
+        <v>1.935385019517287</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1009,28 +1009,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.1701360960301399</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.365979383233586</v>
       </c>
       <c r="H8" t="n">
-        <v>0.74961</v>
+        <v>0.62473</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.103310004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05920015676214896</v>
+        <v>0.1138706654170571</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4725309961522017</v>
+        <v>-0.3660965323336457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1252831184498226</v>
+        <v>0.31104</v>
       </c>
       <c r="M8" t="n">
-        <v>45444575232</v>
+        <v>32211515392</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1049,33 +1049,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6379551334970399</v>
+        <v>0.1793313601752127</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5743773535877754</v>
+        <v>0.3719061223989308</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1083,32 +1083,32 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G9" t="n">
-        <v>0.173598959321368</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.74961</v>
       </c>
       <c r="I9" t="n">
-        <v>0.24063</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1745156346340175</v>
+        <v>0.08768265466652037</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.181678851404915</v>
+        <v>-0.4583470530128415</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9605720934742562</v>
+        <v>0.1913018837803322</v>
       </c>
       <c r="M9" t="n">
-        <v>497267048448</v>
+        <v>44254543872</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1123,33 +1123,33 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1394364870224072</v>
+        <v>0.4235195791463582</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1374513063739387</v>
+        <v>0.5710426099809391</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1157,28 +1157,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1701360960301399</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365979383233586</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H10" t="n">
-        <v>0.62473</v>
+        <v>0.74768996</v>
       </c>
       <c r="I10" t="n">
-        <v>0.103310004</v>
+        <v>0.04249</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09074116832140389</v>
+        <v>0.07897462420002999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3753174786423459</v>
+        <v>-0.3954457508557822</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2417717625346049</v>
+        <v>0.1997103876552508</v>
       </c>
       <c r="M10" t="n">
-        <v>32686991360</v>
+        <v>138930388992</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1197,33 +1197,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2349587040253922</v>
+        <v>0.2450662883614234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.310637124319542</v>
+        <v>0.3174510282628678</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1231,32 +1231,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H11" t="n">
-        <v>0.74768996</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04249</v>
+        <v>0.24063</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0691093496534434</v>
+        <v>0.2072462246043529</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4009733077717151</v>
+        <v>-0.1588744431970449</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1723539904376608</v>
+        <v>1.304465466149988</v>
       </c>
       <c r="M11" t="n">
-        <v>140212355072</v>
+        <v>483785244672</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1271,33 +1271,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3790929445553863</v>
+        <v>0.03767735859507892</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3085680810099776</v>
+        <v>0.123006722604595</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1305,26 +1305,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2391183028460648</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>0.1586149467868072</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1210385188280461</v>
+      </c>
       <c r="H12" t="n">
-        <v>0.68041</v>
+        <v>0.5519500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15755</v>
+        <v>0.13573</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1248888248373548</v>
+        <v>0.2778784911059713</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3737132504323479</v>
+        <v>-0.4212942704534879</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3341835610401054</v>
+        <v>0.6595828868188937</v>
       </c>
       <c r="M12" t="n">
-        <v>127949856768</v>
+        <v>70752649216</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1333,43 +1335,43 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2658147985287158</v>
+        <v>0.07111247860366587</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2275251745239564</v>
+        <v>0.2910769388400953</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.7</v>
+        <v>68.7</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1377,26 +1379,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.4878747583673768</v>
+        <v>0.3291712528765784</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.84796</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04528</v>
+        <v>0.17292999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08944095477386926</v>
+        <v>0.03610797350993389</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4680485762144054</v>
+        <v>-0.4364503311258278</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1910933166323698</v>
+        <v>0.08273100267055138</v>
       </c>
       <c r="M13" t="n">
-        <v>107350425600</v>
+        <v>453577277440</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1415,33 +1417,33 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2098490077226263</v>
+        <v>0.4240984575313709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6972282034917359</v>
+        <v>0.2713861744852626</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1449,26 +1451,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.3291712528765784</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>0.1546194776009138</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3167495145145989</v>
+      </c>
       <c r="H14" t="n">
-        <v>0.84796</v>
+        <v>0.80204004</v>
       </c>
       <c r="I14" t="n">
-        <v>0.17292999</v>
+        <v>0.14166</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0310823008382981</v>
+        <v>-0.0919069356175739</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4391838456266146</v>
+        <v>-0.5935341254490191</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07077286914765908</v>
+        <v>-0.1548469273743017</v>
       </c>
       <c r="M14" t="n">
-        <v>455788101632</v>
+        <v>132765483008</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1477,43 +1481,43 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6795359749968264</v>
+        <v>0.11456723218641</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2853754493566614</v>
+        <v>1.192536042950173</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1521,71 +1525,73 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>0.2230660589034148</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2972340671812952</v>
+      </c>
       <c r="H15" t="n">
-        <v>0.75795</v>
+        <v>0.38952</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04513</v>
+        <v>0.14473</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1015140670361574</v>
+        <v>0.1463225620975162</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4174716283979941</v>
+        <v>-0.3214696412143514</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2431639903906944</v>
+        <v>0.455167590770882</v>
       </c>
       <c r="M15" t="n">
-        <v>45657448448</v>
+        <v>214440476672</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5252395003996511</v>
+        <v>0.04424042185109833</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4804250616635359</v>
+        <v>0.3629104769275096</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1593,73 +1599,71 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1092124213025429</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.1337066930484769</v>
-      </c>
+        <v>0.1539697807235301</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.97725</v>
+        <v>0.75795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1911</v>
+        <v>0.04513</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1414928139800751</v>
+        <v>0.1188338884710434</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2000381076814198</v>
+        <v>-0.4071129257548082</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7073292965029251</v>
+        <v>0.2918941673264716</v>
       </c>
       <c r="M16" t="n">
-        <v>689702764544</v>
+        <v>44859740160</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.09467475906268485</v>
+        <v>0.3489382707421496</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2071664423134003</v>
+        <v>0.4073794580418471</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>Everpure, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1667,28 +1671,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.097332408585459</v>
+        <v>0.0998020993811779</v>
       </c>
       <c r="G17" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.3372469555379434</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.69734</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.03031</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1579714149355704</v>
+        <v>0.04068873983159693</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3648991484765517</v>
+        <v>-0.5948337376908805</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4329180147311898</v>
+        <v>0.06840355086372353</v>
       </c>
       <c r="M17" t="n">
-        <v>26139742208</v>
+        <v>46698467328</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1707,33 +1711,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.197395248425726</v>
+        <v>0.8029074146070754</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3577640494988241</v>
+        <v>1.242957753143294</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1741,37 +1745,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H18" t="n">
-        <v>0.38952</v>
+        <v>0.97725</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14473</v>
+        <v>0.1911</v>
       </c>
       <c r="J18" t="n">
-        <v>0.181934712807706</v>
+        <v>0.1627616869073365</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.298311333095493</v>
+        <v>-0.1851328120667666</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6098820011959337</v>
+        <v>0.879161749288602</v>
       </c>
       <c r="M18" t="n">
-        <v>207363145728</v>
+        <v>677086953472</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1781,33 +1785,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.02883485370679817</v>
+        <v>0.01142061374309455</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3700557048270037</v>
+        <v>0.2037204586726216</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Seagate Technology Holdings PLC</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,26 +1819,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1820341908356484</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>0.097332408585459</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.06564477917470324</v>
+      </c>
       <c r="H19" t="n">
-        <v>0.45576</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.29354998</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2270540885442229</v>
+        <v>0.168271667511404</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7720406182171177</v>
+        <v>-0.3592498732894071</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2940960400096067</v>
+        <v>0.4683972911963883</v>
       </c>
       <c r="M19" t="n">
-        <v>208480731136</v>
+        <v>25909278720</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1843,43 +1849,43 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01962985315181021</v>
+        <v>0.1067172054781858</v>
       </c>
       <c r="S19" t="n">
-        <v>1.424085151046378</v>
+        <v>0.3451967376756433</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.3</v>
+        <v>66.8</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1887,28 +1893,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.1251174560921597</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.3333790189024399</v>
-      </c>
+        <v>0.2391183028460648</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.60897</v>
+        <v>0.68041</v>
       </c>
       <c r="I20" t="n">
-        <v>0.12958999</v>
+        <v>0.15755</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2487077518027447</v>
+        <v>0.1919184839044652</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3142591300302396</v>
+        <v>-0.3419003115264798</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7914097890451514</v>
+        <v>0.5613287775246771</v>
       </c>
       <c r="M20" t="n">
-        <v>4206119354368</v>
+        <v>121764675584</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1917,43 +1921,43 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.02000969543903452</v>
+        <v>0.1792317540257597</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2257818382032553</v>
+        <v>0.0177197985588482</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.2</v>
+        <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1961,28 +1965,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.7634291720222148</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.4181552919037022</v>
       </c>
       <c r="H21" t="n">
-        <v>0.80204004</v>
+        <v>0.108219996</v>
       </c>
       <c r="I21" t="n">
-        <v>0.14166</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.05269549175602461</v>
+        <v>-0.0300984206912337</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5759829355471002</v>
+        <v>-0.5541313801785306</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.091487939145231</v>
+        <v>-0.05431639818256919</v>
       </c>
       <c r="M21" t="n">
-        <v>127269978112</v>
+        <v>28702816256</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1991,7 +1995,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2001,33 +2005,33 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1460852310453788</v>
+        <v>0.6068406682075573</v>
       </c>
       <c r="S21" t="n">
-        <v>1.140688748944991</v>
+        <v>0.8815676106235544</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67.2</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2035,37 +2039,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1586149467868072</v>
+        <v>0.05150438997980311</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1210385188280461</v>
+        <v>0.1218387563505456</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5519500000000001</v>
+        <v>0.88465</v>
       </c>
       <c r="I22" t="n">
-        <v>0.13573</v>
+        <v>0.45124</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3454436424533613</v>
+        <v>0.1251387347391786</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3906964159042877</v>
+        <v>-0.2755965593784683</v>
       </c>
       <c r="L22" t="n">
-        <v>0.884174075807206</v>
+        <v>0.4540649383337526</v>
       </c>
       <c r="M22" t="n">
-        <v>67199614976</v>
+        <v>26064128000</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2075,33 +2079,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.04278970867203258</v>
+        <v>0.1159123581334462</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2966838562556793</v>
+        <v>0.1157805676153218</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="D23" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2109,28 +2113,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.1251174560921597</v>
+        <v>0.1518674545518492</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3333790189024399</v>
+        <v>0.08526334391298396</v>
       </c>
       <c r="H23" t="n">
-        <v>0.60897</v>
+        <v>0.82921</v>
       </c>
       <c r="I23" t="n">
-        <v>0.12958999</v>
+        <v>0.01353</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2382314999413628</v>
+        <v>0.1630536844253929</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3060718892928345</v>
+        <v>-0.2599510104102878</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7783514536136793</v>
+        <v>0.6272477424420887</v>
       </c>
       <c r="M23" t="n">
-        <v>4171386060800</v>
+        <v>93882785792</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2139,7 +2143,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2149,33 +2153,33 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01975381950029775</v>
+        <v>0.1076944085422449</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2164523786460073</v>
+        <v>0.2372773804596557</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.8</v>
+        <v>63.5</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2183,37 +2187,37 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.06564722266304868</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.4161701082120004</v>
       </c>
       <c r="H24" t="n">
-        <v>0.55724</v>
+        <v>0.63802</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05128</v>
+        <v>0.09882000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.01922204779347625</v>
+        <v>0.09813805164077771</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.747347890205033</v>
+        <v>-0.2635531323937865</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.02572034797368964</v>
+        <v>0.3723653395784546</v>
       </c>
       <c r="M24" t="n">
-        <v>1029487722496</v>
+        <v>12311422976</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2223,33 +2227,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2090762380073785</v>
+        <v>0.1354981706742153</v>
       </c>
       <c r="S24" t="n">
-        <v>2.094812738186907</v>
+        <v>0.190277963315008</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64.2</v>
+        <v>62.8</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2257,32 +2261,32 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1483959547833886</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6156160063417289</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H25" t="n">
-        <v>0.55659</v>
+        <v>0.55724</v>
       </c>
       <c r="I25" t="n">
-        <v>0.16832</v>
+        <v>0.05128</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03106893211720085</v>
+        <v>-0.02271931346721134</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3339252562757286</v>
+        <v>-0.703080878989131</v>
       </c>
       <c r="L25" t="n">
-        <v>0.09304157602127176</v>
+        <v>-0.03231394018263803</v>
       </c>
       <c r="M25" t="n">
-        <v>25112223744</v>
+        <v>1034842210304</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2297,33 +2301,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.08914285177712911</v>
+        <v>0.1482836467016857</v>
       </c>
       <c r="S25" t="n">
-        <v>0.342835427282056</v>
+        <v>1.914528612158764</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.09999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2331,37 +2335,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.7634291720222148</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4181552919037022</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H26" t="n">
-        <v>0.108219996</v>
+        <v>0.60081</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07877000000000001</v>
+        <v>0.12174</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.02045769764216365</v>
+        <v>0.07412149665670786</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5496994914470643</v>
+        <v>-0.3360719874804383</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.03721614802354918</v>
+        <v>0.2205524394115777</v>
       </c>
       <c r="M26" t="n">
-        <v>28420321280</v>
+        <v>54222422016</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2371,33 +2375,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4123408262101467</v>
+        <v>0.1510022084178235</v>
       </c>
       <c r="S26" t="n">
-        <v>0.947771278918103</v>
+        <v>0.1929264630230452</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.8</v>
+        <v>61.2</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2405,28 +2409,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.09890131082105791</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1098987103332316</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.57167</v>
       </c>
       <c r="I27" t="n">
-        <v>0.058530003</v>
+        <v>0.04658</v>
       </c>
       <c r="J27" t="n">
-        <v>0.172278674505612</v>
+        <v>0.2604566050888812</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1817210048102619</v>
+        <v>-0.2262112234227954</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9480394117647059</v>
+        <v>1.151386748844376</v>
       </c>
       <c r="M27" t="n">
-        <v>52292333568</v>
+        <v>15471404032</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2435,7 +2439,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2445,33 +2449,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1948353213984786</v>
+        <v>0.08057567301145374</v>
       </c>
       <c r="S27" t="n">
-        <v>0.124408396071563</v>
+        <v>0.1797760846173413</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.4</v>
+        <v>60.9</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2479,104 +2483,106 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.1948193100306586</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>0.09890131082105791</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1098987103332316</v>
+      </c>
       <c r="H28" t="n">
-        <v>0.44244</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05815</v>
+        <v>0.058530003</v>
       </c>
       <c r="J28" t="n">
-        <v>0.220600753995646</v>
+        <v>0.2059946861507804</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.8430308501035416</v>
+        <v>-0.1525517546772944</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2616757784944071</v>
+        <v>1.35032656023222</v>
       </c>
       <c r="M28" t="n">
-        <v>84466008064</v>
+        <v>50492424192</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1525986522629132</v>
+        <v>0.07298890038732697</v>
       </c>
       <c r="S28" t="n">
-        <v>0.3670877484061343</v>
+        <v>0.04974558170422583</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VeriSign, Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.7</v>
+        <v>59.9</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.05150438997980311</v>
+        <v>0.08514371661641951</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1218387563505456</v>
+        <v>0.1477415678186438</v>
       </c>
       <c r="H29" t="n">
-        <v>0.88465</v>
+        <v>0.5099000299999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.45124</v>
+        <v>0.16655001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1293298520452566</v>
+        <v>0.1310356439747176</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2728981723237598</v>
+        <v>-0.1650606154802612</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4739124888378614</v>
+        <v>0.7938637790332697</v>
       </c>
       <c r="M29" t="n">
-        <v>25967400960</v>
+        <v>77114769408</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2591,71 +2597,71 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.127037152405824</v>
+        <v>0.08573495614748827</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1517527763041562</v>
+        <v>0.1130412112019656</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.5</v>
+        <v>58.5</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.06564722266304868</v>
+        <v>0.03534983888485344</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4161701082120004</v>
+        <v>0.388859258627138</v>
       </c>
       <c r="H30" t="n">
-        <v>0.63802</v>
+        <v>0.19910999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09882000000000001</v>
+        <v>0.08643000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.09892938027589038</v>
+        <v>0.0381142003839865</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2630224418365246</v>
+        <v>-0.8040603000782194</v>
       </c>
       <c r="L30" t="n">
-        <v>0.376125244618395</v>
+        <v>0.04740216670351555</v>
       </c>
       <c r="M30" t="n">
-        <v>12302558208</v>
+        <v>357657378816</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2665,62 +2671,60 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1489059241095896</v>
+        <v>0.3682602387051102</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1885476006334648</v>
+        <v>2.241342812821664</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>62.4</v>
+        <v>58.4</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.142358869424539</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.1945038186480894</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.60081</v>
+        <v>0.75185996</v>
       </c>
       <c r="I31" t="n">
-        <v>0.12174</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02672196913034619</v>
+        <v>-0.1250555473263221</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.3653702318623785</v>
+        <v>-0.6827136720485854</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07313668930864453</v>
+        <v>-0.1831742243436755</v>
       </c>
       <c r="M31" t="n">
-        <v>56725651456</v>
+        <v>276503363584</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2729,24 +2733,24 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2699627827822078</v>
+        <v>0.3543986454591597</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2563517364617405</v>
+        <v>1.706354097500268</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-27 12:53:19</t>
+          <t>2026-10-04 13:06:39</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -418,25 +418,25 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>89.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -577,16 +577,16 @@
         <v>0.53572</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4007266509938021</v>
+        <v>0.433692210397767</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2978414191066466</v>
+        <v>-0.2835397766922539</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345436280137773</v>
+        <v>1.529563913244117</v>
       </c>
       <c r="M2" t="n">
-        <v>5649190617088</v>
+        <v>5536424132608</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1977078628548592</v>
+        <v>0.1277775363521345</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3218599940218567</v>
+        <v>0.2182795269998112</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81.7</v>
+        <v>80.8</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2714652572159764</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3708447402164197</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.63004</v>
+        <v>0.77282</v>
       </c>
       <c r="I3" t="n">
-        <v>0.14119</v>
+        <v>0.05704</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1681082228116713</v>
+        <v>0.2366811417099464</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4476971304557511</v>
+        <v>-0.3614105529612011</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3754954217386625</v>
+        <v>0.6548816568047339</v>
       </c>
       <c r="M3" t="n">
-        <v>261514952704</v>
+        <v>188573990912</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1966182338656004</v>
+        <v>0.3405741155901671</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6368014335649153</v>
+        <v>0.3950383549836396</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.2714652572159764</v>
       </c>
       <c r="G4" t="n">
-        <v>2.336504917866317</v>
+        <v>0.3708447402164197</v>
       </c>
       <c r="H4" t="n">
-        <v>0.77282</v>
+        <v>0.63004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05704</v>
+        <v>0.14119</v>
       </c>
       <c r="J4" t="n">
-        <v>0.207383143721505</v>
+        <v>0.1243425302205408</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3765392645617623</v>
+        <v>-0.4716249884654425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5507610048659048</v>
+        <v>0.2636470358051262</v>
       </c>
       <c r="M4" t="n">
-        <v>193149878272</v>
+        <v>273357848576</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -753,14 +753,14 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4192749211426474</v>
+        <v>0.1964670869214442</v>
       </c>
       <c r="S4" t="n">
-        <v>0.262416822895835</v>
+        <v>0.4709195555845509</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -799,16 +799,16 @@
         <v>0.14088</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1184326512472706</v>
+        <v>0.09823723998729128</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.325256506869167</v>
+        <v>-0.347375109798718</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3641207746688053</v>
+        <v>0.2827987302953674</v>
       </c>
       <c r="M5" t="n">
-        <v>3842942959616</v>
+        <v>3973186846720</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -827,66 +827,66 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3407051562809811</v>
+        <v>0.3710767071995553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3913867942988862</v>
+        <v>0.4485895043944712</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1989383144293926</v>
+        <v>0.1231541137431111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.398395285030712</v>
+        <v>0.3232467390277567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.81747</v>
+        <v>0.84501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14591</v>
+        <v>0.11537</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09185899901109762</v>
+        <v>0.03368475186423248</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2854356664102846</v>
+        <v>-0.4420159424016457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3218203252814933</v>
+        <v>0.07620709714950559</v>
       </c>
       <c r="M6" t="n">
-        <v>1854788337664</v>
+        <v>21123534848</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -901,14 +901,14 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2138377464221191</v>
+        <v>0.5503906855931455</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2695921368463412</v>
+        <v>0.4572091830830529</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -947,16 +947,16 @@
         <v>0.44557</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4141183749034785</v>
+        <v>0.5113026239067056</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8329038320200206</v>
+        <v>-0.8189990281827016</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4971983066750067</v>
+        <v>0.6243018688816375</v>
       </c>
       <c r="M7" t="n">
-        <v>1213973397504</v>
+        <v>1164234457088</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -975,14 +975,14 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09153593769833712</v>
+        <v>0.09818569903948782</v>
       </c>
       <c r="S7" t="n">
-        <v>1.935385019517287</v>
+        <v>1.44693940553742</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>73.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1021,16 +1021,16 @@
         <v>0.103310004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1138706654170571</v>
+        <v>0.1441061704910238</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3660965323336457</v>
+        <v>-0.3566757817144216</v>
       </c>
       <c r="L8" t="n">
-        <v>0.31104</v>
+        <v>0.4040256666666671</v>
       </c>
       <c r="M8" t="n">
-        <v>32211515392</v>
+        <v>31739813888</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1049,33 +1049,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1793313601752127</v>
+        <v>0.1016372271292281</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3719061223989308</v>
+        <v>0.313808263366427</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>72.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1083,32 +1083,32 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H9" t="n">
-        <v>0.74961</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.24063</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08768265466652037</v>
+        <v>0.1339666293240995</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4583470530128415</v>
+        <v>-0.2115286689072207</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1913018837803322</v>
+        <v>0.633326111378591</v>
       </c>
       <c r="M9" t="n">
-        <v>44254543872</v>
+        <v>516092493824</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1123,14 +1123,14 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4235195791463582</v>
+        <v>0.09732773009507811</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5710426099809391</v>
+        <v>0.1852207759134394</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1169,16 +1169,16 @@
         <v>0.04249</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07897462420002999</v>
+        <v>0.04168493539684781</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3954457508557822</v>
+        <v>-0.4232571347437173</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1997103876552508</v>
+        <v>0.09848607849714829</v>
       </c>
       <c r="M10" t="n">
-        <v>138930388992</v>
+        <v>145629806592</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1197,33 +1197,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2450662883614234</v>
+        <v>0.2660434828850522</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3174510282628678</v>
+        <v>0.6971084410885731</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1231,32 +1231,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.1989383144293926</v>
       </c>
       <c r="G11" t="n">
-        <v>0.173598959321368</v>
+        <v>0.398395285030712</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.81747</v>
       </c>
       <c r="I11" t="n">
-        <v>0.24063</v>
+        <v>0.14591</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2072462246043529</v>
+        <v>0.11176924040241</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1588744431970449</v>
+        <v>-0.2760794244924653</v>
       </c>
       <c r="L11" t="n">
-        <v>1.304465466149988</v>
+        <v>0.4048445138853888</v>
       </c>
       <c r="M11" t="n">
-        <v>483785244672</v>
+        <v>1830816186368</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1271,33 +1271,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03767735859507892</v>
+        <v>0.09517941837972588</v>
       </c>
       <c r="S11" t="n">
-        <v>0.123006722604595</v>
+        <v>0.14295841365801</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1305,28 +1305,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1586149467868072</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1210385188280461</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.5519500000000001</v>
+        <v>0.84796</v>
       </c>
       <c r="I12" t="n">
-        <v>0.13573</v>
+        <v>0.17292999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2778784911059713</v>
+        <v>-0.02726620425735482</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4212942704534879</v>
+        <v>-0.4911743602009089</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6595828868188937</v>
+        <v>-0.05551227113361926</v>
       </c>
       <c r="M12" t="n">
-        <v>70752649216</v>
+        <v>502359359488</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1335,43 +1333,43 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07111247860366587</v>
+        <v>0.6075823888407603</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2910769388400953</v>
+        <v>0.6324379746775113</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1379,71 +1377,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.3291712528765784</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>0.2230660589034148</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2972340671812952</v>
+      </c>
       <c r="H13" t="n">
-        <v>0.84796</v>
+        <v>0.38952</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17292999</v>
+        <v>0.14473</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03610797350993389</v>
+        <v>0.1652669646950939</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4364503311258278</v>
+        <v>-0.3236474094452085</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08273100267055138</v>
+        <v>0.5106389233221179</v>
       </c>
       <c r="M13" t="n">
-        <v>453577277440</v>
+        <v>215130947584</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4240984575313709</v>
+        <v>0.120267989140924</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2713861744852626</v>
+        <v>0.2434404874971101</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67.7</v>
+        <v>69.5</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1451,28 +1451,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H14" t="n">
-        <v>0.80204004</v>
+        <v>0.74961</v>
       </c>
       <c r="I14" t="n">
-        <v>0.14166</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0919069356175739</v>
+        <v>0.003063012865971215</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5935341254490191</v>
+        <v>-0.500050653429237</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1548469273743017</v>
+        <v>0.006125405186386117</v>
       </c>
       <c r="M14" t="n">
-        <v>132765483008</v>
+        <v>47946067968</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1491,33 +1491,33 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.11456723218641</v>
+        <v>0.5046491974811873</v>
       </c>
       <c r="S14" t="n">
-        <v>1.192536042950173</v>
+        <v>0.9555571498761199</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1525,37 +1525,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H15" t="n">
-        <v>0.38952</v>
+        <v>0.80204004</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14473</v>
+        <v>0.14166</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1463225620975162</v>
+        <v>-0.1562544801026958</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3214696412143514</v>
+        <v>-0.6223363286264442</v>
       </c>
       <c r="L15" t="n">
-        <v>0.455167590770882</v>
+        <v>-0.2510772277227724</v>
       </c>
       <c r="M15" t="n">
-        <v>214440476672</v>
+        <v>142890729472</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1565,14 +1565,14 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04424042185109833</v>
+        <v>0.212489141578615</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3629104769275096</v>
+        <v>1.539113529970789</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         <v>0.04513</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1188338884710434</v>
+        <v>0.1147252264322847</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4071129257548082</v>
+        <v>-0.4085427943619702</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2918941673264716</v>
+        <v>0.2808156893611438</v>
       </c>
       <c r="M16" t="n">
-        <v>44859740160</v>
+        <v>44968189952</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1637,33 +1637,33 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3489382707421496</v>
+        <v>0.2879823471171874</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4073794580418471</v>
+        <v>0.6585777452256945</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Everpure, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.2</v>
+        <v>67.7</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1671,32 +1671,32 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.0998020993811779</v>
+        <v>0.08087962506974211</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3372469555379434</v>
+        <v>0.6534957812135467</v>
       </c>
       <c r="H17" t="n">
-        <v>0.69734</v>
+        <v>0.90433</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03031</v>
+        <v>0.061079998</v>
       </c>
       <c r="J17" t="n">
-        <v>0.04068873983159693</v>
+        <v>0.2258144920137115</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5948337376908805</v>
+        <v>-0.3241193202538108</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06840355086372353</v>
+        <v>0.6967017326732668</v>
       </c>
       <c r="M17" t="n">
-        <v>46698467328</v>
+        <v>32912455680</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1711,33 +1711,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8029074146070754</v>
+        <v>0.03382643585774558</v>
       </c>
       <c r="S17" t="n">
-        <v>1.242957753143294</v>
+        <v>0.2065341010559005</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66.90000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1745,70 +1745,68 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1092124213025429</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.1337066930484769</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.97725</v>
+        <v>0.52216</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1911</v>
+        <v>0.04125</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1627616869073365</v>
+        <v>0.2278182214472539</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1851328120667666</v>
+        <v>-0.7432069165940134</v>
       </c>
       <c r="L18" t="n">
-        <v>0.879161749288602</v>
+        <v>0.3065340436971507</v>
       </c>
       <c r="M18" t="n">
-        <v>677086953472</v>
+        <v>247395418112</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.01142061374309455</v>
+        <v>0.2657571087829507</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2037204586726216</v>
+        <v>1.143420217053858</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
       <c r="D19" t="n">
         <v>67</v>
@@ -1819,37 +1817,37 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.097332408585459</v>
+        <v>0.1092124213025429</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.1337066930484769</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.97725</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.1911</v>
       </c>
       <c r="J19" t="n">
-        <v>0.168271667511404</v>
+        <v>0.08868050330782196</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3592498732894071</v>
+        <v>-0.2375405370346348</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4683972911963883</v>
+        <v>0.3733278724333767</v>
       </c>
       <c r="M19" t="n">
-        <v>25909278720</v>
+        <v>723626622976</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1859,33 +1857,33 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1067172054781858</v>
+        <v>0.07943003914019764</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3451967376756433</v>
+        <v>0.2714110273822299</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.8</v>
+        <v>64.7</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1893,68 +1891,70 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.2391183028460648</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
+        <v>0.097332408585459</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.06564477917470324</v>
+      </c>
       <c r="H20" t="n">
-        <v>0.68041</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.15755</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1919184839044652</v>
+        <v>0.1585243264977885</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3419003115264798</v>
+        <v>-0.3645958986731002</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5613287775246771</v>
+        <v>0.4347945960849185</v>
       </c>
       <c r="M20" t="n">
-        <v>121764675584</v>
+        <v>26127269888</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1792317540257597</v>
+        <v>0.0990444017868537</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0177197985588482</v>
+        <v>0.3140046596170787</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>64</v>
@@ -1965,37 +1965,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.7634291720222148</v>
+        <v>0.1518674545518492</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4181552919037022</v>
+        <v>0.08526334391298396</v>
       </c>
       <c r="H21" t="n">
-        <v>0.108219996</v>
+        <v>0.82921</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07877000000000001</v>
+        <v>0.01353</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0300984206912337</v>
+        <v>0.118788995862664</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5541313801785306</v>
+        <v>-0.2891037079158415</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.05431639818256919</v>
+        <v>0.4108871405317418</v>
       </c>
       <c r="M21" t="n">
-        <v>28702816256</v>
+        <v>97732771840</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2005,30 +2005,30 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6068406682075573</v>
+        <v>0.1755796911718506</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8815676106235544</v>
+        <v>0.3001988653162082</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VeriSign, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64</v>
+        <v>64.3</v>
       </c>
       <c r="D22" t="n">
         <v>64</v>
@@ -2039,37 +2039,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.05150438997980311</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1218387563505456</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H22" t="n">
-        <v>0.88465</v>
+        <v>0.55724</v>
       </c>
       <c r="I22" t="n">
-        <v>0.45124</v>
+        <v>0.05128</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1251387347391786</v>
+        <v>0.04622266074658765</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2755965593784683</v>
+        <v>-0.6904785397138629</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4540649383337526</v>
+        <v>0.06694293607697425</v>
       </c>
       <c r="M22" t="n">
-        <v>26064128000</v>
+        <v>992708001792</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2079,30 +2079,30 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1159123581334462</v>
+        <v>0.1379328934242756</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1157805676153218</v>
+        <v>1.481635619683764</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.8</v>
+        <v>64.3</v>
       </c>
       <c r="D23" t="n">
         <v>64</v>
@@ -2113,37 +2113,37 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.1518674545518492</v>
+        <v>0.7634291720222148</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08526334391298396</v>
+        <v>0.4181552919037022</v>
       </c>
       <c r="H23" t="n">
-        <v>0.82921</v>
+        <v>0.108219996</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01353</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1630536844253929</v>
+        <v>0.009835622984111891</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2599510104102878</v>
+        <v>-0.5345836817584517</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6272477424420887</v>
+        <v>0.01839865921787724</v>
       </c>
       <c r="M23" t="n">
-        <v>93882785792</v>
+        <v>27497285632</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2153,26 +2153,26 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1076944085422449</v>
+        <v>0.5133767476961146</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2372773804596557</v>
+        <v>0.6571654881653397</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Everpure, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2187,32 +2187,32 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.06564722266304868</v>
+        <v>0.0998020993811779</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4161701082120004</v>
+        <v>0.3372469555379434</v>
       </c>
       <c r="H24" t="n">
-        <v>0.63802</v>
+        <v>0.69734</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09882000000000001</v>
+        <v>0.03031</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09813805164077771</v>
+        <v>-0.04405333678555245</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2635531323937865</v>
+        <v>-0.6324681209139751</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3723653395784546</v>
+        <v>-0.06965305495855079</v>
       </c>
       <c r="M24" t="n">
-        <v>12311422976</v>
+        <v>51480281088</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2227,33 +2227,33 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1354981706742153</v>
+        <v>1.050026595566973</v>
       </c>
       <c r="S24" t="n">
-        <v>0.190277963315008</v>
+        <v>1.53511665531042</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2261,32 +2261,32 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H25" t="n">
-        <v>0.55724</v>
+        <v>0.60081</v>
       </c>
       <c r="I25" t="n">
-        <v>0.05128</v>
+        <v>0.12174</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.02271931346721134</v>
+        <v>0.1253540020867492</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.703080878989131</v>
+        <v>-0.3044045312267105</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.03231394018263803</v>
+        <v>0.4118007100012241</v>
       </c>
       <c r="M25" t="n">
-        <v>1034842210304</v>
+        <v>51753906176</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2301,33 +2301,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1482836467016857</v>
+        <v>0.1058625572510443</v>
       </c>
       <c r="S25" t="n">
-        <v>1.914528612158764</v>
+        <v>0.05333975777768529</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.4</v>
+        <v>60.5</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2335,28 +2335,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.142358869424539</v>
+        <v>0.06564722266304868</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1945038186480894</v>
+        <v>0.4161701082120004</v>
       </c>
       <c r="H26" t="n">
-        <v>0.60081</v>
+        <v>0.63802</v>
       </c>
       <c r="I26" t="n">
-        <v>0.12174</v>
+        <v>0.09882000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07412149665670786</v>
+        <v>0.0229995208433158</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3360719874804383</v>
+        <v>-0.3139434595112601</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2205524394115777</v>
+        <v>0.07326007326007339</v>
       </c>
       <c r="M26" t="n">
-        <v>54222422016</v>
+        <v>13215687680</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2375,33 +2375,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1510022084178235</v>
+        <v>0.148470149385324</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1929264630230452</v>
+        <v>0.3160549535784689</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.2</v>
+        <v>60.5</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2409,28 +2409,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.0405993172034298</v>
+        <v>0.09890131082105791</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5822968332827563</v>
+        <v>0.1098987103332316</v>
       </c>
       <c r="H27" t="n">
-        <v>0.57167</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04658</v>
+        <v>0.058530003</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2604566050888812</v>
+        <v>0.1605712760277629</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2262112234227954</v>
+        <v>-0.1825947677522691</v>
       </c>
       <c r="L27" t="n">
-        <v>1.151386748844376</v>
+        <v>0.8793859649122802</v>
       </c>
       <c r="M27" t="n">
-        <v>15471404032</v>
+        <v>52348227584</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2449,33 +2449,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.08057567301145374</v>
+        <v>0.05331909101931886</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1797760846173413</v>
+        <v>0.1340021617826392</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.9</v>
+        <v>60.2</v>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2483,37 +2483,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.09890131082105791</v>
+        <v>0.05150438997980311</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1098987103332316</v>
+        <v>0.1218387563505456</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.88465</v>
       </c>
       <c r="I28" t="n">
-        <v>0.058530003</v>
+        <v>0.45124</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2059946861507804</v>
+        <v>0.06801870020412193</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1525517546772944</v>
+        <v>-0.3123724237834991</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35032656023222</v>
+        <v>0.2177487352445193</v>
       </c>
       <c r="M28" t="n">
-        <v>50492424192</v>
+        <v>27458095104</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2523,107 +2523,105 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.07298890038732697</v>
+        <v>0.1269713176320513</v>
       </c>
       <c r="S28" t="n">
-        <v>0.04974558170422583</v>
+        <v>0.1757718247421718</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.08514371661641951</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.1477415678186438</v>
-      </c>
+        <v>0.2772574009717286</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.5099000299999999</v>
+        <v>0.52225</v>
       </c>
       <c r="I29" t="n">
-        <v>0.16655001</v>
+        <v>0.029719999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1310356439747176</v>
+        <v>0.3091433587786259</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1650606154802612</v>
+        <v>-0.2707379134860051</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7938637790332697</v>
+        <v>1.14185469924812</v>
       </c>
       <c r="M29" t="n">
-        <v>77114769408</v>
+        <v>85143044096</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.08573495614748827</v>
+        <v>0.03655637710626336</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1130412112019656</v>
+        <v>0.2878489817923586</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>58.5</v>
+        <v>59.2</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2631,28 +2629,26 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.03534983888485344</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.388859258627138</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.19910999</v>
+        <v>0.75185996</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08643000000000001</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0381142003839865</v>
+        <v>-0.1267815590459571</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.8040603000782194</v>
+        <v>-0.6884816753926701</v>
       </c>
       <c r="L30" t="n">
-        <v>0.04740216670351555</v>
+        <v>-0.1841465990705537</v>
       </c>
       <c r="M30" t="n">
-        <v>357657378816</v>
+        <v>281623035904</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2661,43 +2657,43 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3682602387051102</v>
+        <v>0.4636794379477818</v>
       </c>
       <c r="S30" t="n">
-        <v>2.241342812821664</v>
+        <v>1.902643834280737</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>ResMed Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2705,52 +2701,54 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>0.1021250802553491</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1426549686403549</v>
+      </c>
       <c r="H31" t="n">
-        <v>0.75185996</v>
+        <v>0.6161799999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0078100003</v>
+        <v>0.14002</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1250555473263221</v>
+        <v>0.08768941534449026</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.6827136720485854</v>
+        <v>-0.2163877417952619</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.1831742243436755</v>
+        <v>0.4052420650863798</v>
       </c>
       <c r="M31" t="n">
-        <v>276503363584</v>
+        <v>32354060288</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3543986454591597</v>
+        <v>0.1622679144421717</v>
       </c>
       <c r="S31" t="n">
-        <v>1.706354097500268</v>
+        <v>0.01103791855664848</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-10-04 13:06:39</t>
+          <t>2026-10-11 13:53:24</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -418,18 +418,18 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
@@ -545,19 +545,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.000450949944396</v>
+        <v>0.09820006113830493</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04239508347386</v>
+        <v>2.336504917866317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74674004</v>
+        <v>0.77282</v>
       </c>
       <c r="I2" t="n">
-        <v>0.53572</v>
+        <v>0.05704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.433692210397767</v>
+        <v>0.1868532197756543</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2835397766922539</v>
+        <v>-0.3921063564603241</v>
       </c>
       <c r="L2" t="n">
-        <v>1.529563913244117</v>
+        <v>0.476537084127993</v>
       </c>
       <c r="M2" t="n">
-        <v>5536424132608</v>
+        <v>198096093184</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -605,33 +605,33 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1277775363521345</v>
+        <v>0.387441522269363</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2182795269998112</v>
+        <v>0.3272525767371199</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.8</v>
+        <v>79.3</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -639,37 +639,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.09820006113830493</v>
+        <v>0.1612397915820203</v>
       </c>
       <c r="G3" t="n">
-        <v>2.336504917866317</v>
+        <v>0.2285599828574523</v>
       </c>
       <c r="H3" t="n">
-        <v>0.77282</v>
+        <v>0.67944</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05704</v>
+        <v>0.14088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2366811417099464</v>
+        <v>0.1326671392117948</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3614105529612011</v>
+        <v>-0.3399489651261696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6548816568047339</v>
+        <v>0.3902560467055883</v>
       </c>
       <c r="M3" t="n">
-        <v>188573990912</v>
+        <v>3928485003264</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -679,33 +679,33 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3405741155901671</v>
+        <v>0.3175716912141924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3950383549836396</v>
+        <v>0.2564013495513537</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Everpure, Inc.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.8</v>
+        <v>78.8</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.2714652572159764</v>
+        <v>0.0998020993811779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3708447402164197</v>
+        <v>0.3372469555379434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.63004</v>
+        <v>0.69734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14119</v>
+        <v>0.03031</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1243425302205408</v>
+        <v>0.218492540924119</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4716249884654425</v>
+        <v>-0.5421336988952503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2636470358051262</v>
+        <v>0.4030233526699389</v>
       </c>
       <c r="M4" t="n">
-        <v>273357848576</v>
+        <v>41323511808</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -753,33 +753,33 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1964670869214442</v>
+        <v>0.773344796153991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4709195555845509</v>
+        <v>0.8517246509754277</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -787,54 +787,52 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1612397915820203</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2285599828574523</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.67944</v>
+        <v>0.84796</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14088</v>
+        <v>0.17292999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09823723998729128</v>
+        <v>0.1096432295866259</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.347375109798718</v>
+        <v>-0.4282105036822018</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2827987302953674</v>
+        <v>0.2560498368064275</v>
       </c>
       <c r="M5" t="n">
-        <v>3973186846720</v>
+        <v>447040946176</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3710767071995553</v>
+        <v>0.3795327427459936</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4485895043944712</v>
+        <v>0.2707835204243567</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
@@ -850,14 +848,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -873,16 +871,16 @@
         <v>0.11537</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03368475186423248</v>
+        <v>0.04155871074722772</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4420159424016457</v>
+        <v>-0.4377655715618198</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07620709714950559</v>
+        <v>0.0949337121212122</v>
       </c>
       <c r="M6" t="n">
-        <v>21123534848</v>
+        <v>20963846144</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -901,62 +899,62 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5503906855931455</v>
+        <v>0.545942424872498</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4572091830830529</v>
+        <v>0.3809931883606477</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.06713489726936261</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.006929629272242499</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.80716</v>
+        <v>0.74768996</v>
       </c>
       <c r="I7" t="n">
-        <v>0.44557</v>
+        <v>0.04249</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5113026239067056</v>
+        <v>0.07228104529125878</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8189990281827016</v>
+        <v>-0.427766429527365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6243018688816375</v>
+        <v>0.1689731598880291</v>
       </c>
       <c r="M7" t="n">
-        <v>1164234457088</v>
+        <v>146777391104</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -965,7 +963,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -975,14 +973,14 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09818569903948782</v>
+        <v>0.3559694876675608</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44693940553742</v>
+        <v>0.4687564229459595</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
@@ -998,14 +996,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>71.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>High Conviction</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1021,16 +1019,16 @@
         <v>0.103310004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1441061704910238</v>
+        <v>0.1211243607624359</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3566757817144216</v>
+        <v>-0.3711064621106462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4040256666666671</v>
+        <v>0.3263870967741931</v>
       </c>
       <c r="M8" t="n">
-        <v>31739813888</v>
+        <v>32468121600</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1049,33 +1047,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1016372271292281</v>
+        <v>0.1367419492704247</v>
       </c>
       <c r="S8" t="n">
-        <v>0.313808263366427</v>
+        <v>0.3447952724464796</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>71.5</v>
+        <v>74.7</v>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1083,32 +1081,32 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1382198495222513</v>
+        <v>0.3168737488062043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.173598959321368</v>
+        <v>0.5171329563234539</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.83399004</v>
       </c>
       <c r="I9" t="n">
-        <v>0.24063</v>
+        <v>0.20357001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1339666293240995</v>
+        <v>0.05650199279253476</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2115286689072207</v>
+        <v>-0.368495580853281</v>
       </c>
       <c r="L9" t="n">
-        <v>0.633326111378591</v>
+        <v>0.1533315342933011</v>
       </c>
       <c r="M9" t="n">
-        <v>516092493824</v>
+        <v>1120462569472</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1123,33 +1121,33 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09732773009507811</v>
+        <v>0.0975946286709144</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1852207759134394</v>
+        <v>0.3602561525872414</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1157,32 +1155,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.1382198495222513</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.173598959321368</v>
       </c>
       <c r="H10" t="n">
-        <v>0.74768996</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04249</v>
+        <v>0.24063</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04168493539684781</v>
+        <v>0.08855349680930336</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4232571347437173</v>
+        <v>-0.2476434193903664</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09848607849714829</v>
+        <v>0.3575846958796604</v>
       </c>
       <c r="M10" t="n">
-        <v>145629806592</v>
+        <v>540866019328</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1197,30 +1195,30 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2660434828850522</v>
+        <v>0.1295410142455946</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6971084410885731</v>
+        <v>0.1881690844923272</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>70</v>
@@ -1231,32 +1229,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1989383144293926</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G11" t="n">
-        <v>0.398395285030712</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H11" t="n">
-        <v>0.81747</v>
+        <v>0.55724</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14591</v>
+        <v>0.05128</v>
       </c>
       <c r="J11" t="n">
-        <v>0.11176924040241</v>
+        <v>0.1870541843971631</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2760794244924653</v>
+        <v>-0.6440283687943262</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4048445138853888</v>
+        <v>0.2904440137432826</v>
       </c>
       <c r="M11" t="n">
-        <v>1830816186368</v>
+        <v>863171182592</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1271,33 +1269,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.09517941837972588</v>
+        <v>0.05000296345999278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.14295841365801</v>
+        <v>0.8993138121987871</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1305,26 +1303,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.3291712528765784</v>
+        <v>0.2391183028460648</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.84796</v>
+        <v>0.68041</v>
       </c>
       <c r="I12" t="n">
-        <v>0.17292999</v>
+        <v>0.15755</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02726620425735482</v>
+        <v>0.155143338954469</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4911743602009089</v>
+        <v>-0.3587689713322091</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.05551227113361926</v>
+        <v>0.4324324324324329</v>
       </c>
       <c r="M12" t="n">
-        <v>502359359488</v>
+        <v>124967903232</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1343,33 +1341,33 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6075823888407603</v>
+        <v>0.3323641602816754</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6324379746775113</v>
+        <v>0.02252696549533506</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1377,37 +1375,37 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.2230660589034148</v>
+        <v>0.1402968452680178</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2972340671812952</v>
+        <v>0.2194365698361114</v>
       </c>
       <c r="H13" t="n">
-        <v>0.38952</v>
+        <v>0.74961</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14473</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1652669646950939</v>
+        <v>-0.04292740688233021</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3236474094452085</v>
+        <v>-0.5229733213042917</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5106389233221179</v>
+        <v>-0.08208335900437437</v>
       </c>
       <c r="M13" t="n">
-        <v>215130947584</v>
+        <v>50250027008</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1417,33 +1415,33 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.120267989140924</v>
+        <v>0.5721593617047918</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2434404874971101</v>
+        <v>0.8479308781839834</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1451,28 +1449,26 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1402968452680178</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.2194365698361114</v>
-      </c>
+        <v>0.1539697807235301</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.74961</v>
+        <v>0.75795</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.04513</v>
       </c>
       <c r="J14" t="n">
-        <v>0.003063012865971215</v>
+        <v>0.08964624495571516</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.500050653429237</v>
+        <v>-0.4216236046328808</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006125405186386117</v>
+        <v>0.2126215040397764</v>
       </c>
       <c r="M14" t="n">
-        <v>47946067968</v>
+        <v>45985210368</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1481,40 +1477,40 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5046491974811873</v>
+        <v>0.296087460782881</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9555571498761199</v>
+        <v>0.5409028081815104</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D15" t="n">
         <v>69</v>
@@ -1525,28 +1521,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.06713489726936261</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3167495145145989</v>
+        <v>-0.006929629272242499</v>
       </c>
       <c r="H15" t="n">
-        <v>0.80204004</v>
+        <v>0.80716</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14166</v>
+        <v>0.44557</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1562544801026958</v>
+        <v>0.775710254426289</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6223363286264442</v>
+        <v>-0.7810750534795867</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2510772277227724</v>
+        <v>0.993131519142241</v>
       </c>
       <c r="M15" t="n">
-        <v>142890729472</v>
+        <v>994340044800</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1555,7 +1551,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1565,33 +1561,33 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.212489141578615</v>
+        <v>0.01561978706208844</v>
       </c>
       <c r="S15" t="n">
-        <v>1.539113529970789</v>
+        <v>0.9318203848570095</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1599,26 +1595,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1539697807235301</v>
+        <v>0.1144958764235571</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.75795</v>
+        <v>0.52216</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04513</v>
+        <v>0.04125</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1147252264322847</v>
+        <v>0.4895203441162268</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4085427943619702</v>
+        <v>-0.6897247948031426</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2808156893611438</v>
+        <v>0.7097328496881758</v>
       </c>
       <c r="M16" t="n">
-        <v>44968189952</v>
+        <v>204751880192</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1637,30 +1633,30 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2879823471171874</v>
+        <v>0.1689739530034025</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6585777452256945</v>
+        <v>0.6317273205837473</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.7</v>
+        <v>68.5</v>
       </c>
       <c r="D17" t="n">
         <v>68</v>
@@ -1671,37 +1667,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.03534983888485344</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.388859258627138</v>
       </c>
       <c r="H17" t="n">
-        <v>0.90433</v>
+        <v>0.19910999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.061079998</v>
+        <v>0.08643000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2258144920137115</v>
+        <v>0.3127891788979655</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3241193202538108</v>
+        <v>-0.7559938898851033</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6967017326732668</v>
+        <v>0.4137456440891388</v>
       </c>
       <c r="M17" t="n">
-        <v>32912455680</v>
+        <v>287202967552</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1711,33 +1707,33 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03382643585774558</v>
+        <v>0.1848130923411886</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2065341010559005</v>
+        <v>1.309114152270682</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1745,26 +1741,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>0.1546194776009138</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3167495145145989</v>
+      </c>
       <c r="H18" t="n">
-        <v>0.52216</v>
+        <v>0.80204004</v>
       </c>
       <c r="I18" t="n">
-        <v>0.04125</v>
+        <v>0.14166</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2278182214472539</v>
+        <v>-0.007240525039910128</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7432069165940134</v>
+        <v>-0.5651274167799918</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3065340436971507</v>
+        <v>-0.01281219920485457</v>
       </c>
       <c r="M18" t="n">
-        <v>247395418112</v>
+        <v>124092997632</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1773,24 +1771,24 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2657571087829507</v>
+        <v>0.05468947517511302</v>
       </c>
       <c r="S18" t="n">
-        <v>1.143420217053858</v>
+        <v>1.06659350502082</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
@@ -1829,20 +1827,20 @@
         <v>0.1911</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08868050330782196</v>
+        <v>0.05006589503489711</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2375405370346348</v>
+        <v>-0.2700380020367106</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3733278724333767</v>
+        <v>0.1854031456953635</v>
       </c>
       <c r="M19" t="n">
-        <v>723626622976</v>
+        <v>755841957888</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1857,30 +1855,30 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.07943003914019764</v>
+        <v>0.1186674681421549</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2714110273822299</v>
+        <v>0.2749799780563169</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D20" t="n">
         <v>65</v>
@@ -1891,28 +1889,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.097332408585459</v>
+        <v>0.08087962506974211</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.6534957812135467</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.90433</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.061079998</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1585243264977885</v>
+        <v>0.1633253157985812</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3645958986731002</v>
+        <v>-0.3585741477764318</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4347945960849185</v>
+        <v>0.4554854743750609</v>
       </c>
       <c r="M20" t="n">
-        <v>26127269888</v>
+        <v>34679590912</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1921,7 +1919,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1931,33 +1929,33 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0990444017868537</v>
+        <v>0.09161981300347244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3140046596170787</v>
+        <v>0.09081003438218738</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1965,32 +1963,30 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.1518674545518492</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.08526334391298396</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.82921</v>
+        <v>0.75185996</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01353</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J21" t="n">
-        <v>0.118788995862664</v>
+        <v>0.08250142926250059</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2891037079158415</v>
+        <v>-0.6232024275473855</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4108871405317418</v>
+        <v>0.1323830357772917</v>
       </c>
       <c r="M21" t="n">
-        <v>97732771840</v>
+        <v>232832548864</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1999,36 +1995,36 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1755796911718506</v>
+        <v>0.1455992397434827</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3001988653162082</v>
+        <v>1.145441611909709</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="D22" t="n">
         <v>64</v>
@@ -2039,37 +2035,37 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.1518674545518492</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.08526334391298396</v>
       </c>
       <c r="H22" t="n">
-        <v>0.55724</v>
+        <v>0.82921</v>
       </c>
       <c r="I22" t="n">
-        <v>0.05128</v>
+        <v>0.01353</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04622266074658765</v>
+        <v>0.2845302773684095</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6904785397138629</v>
+        <v>-0.202538327871016</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06694293607697425</v>
+        <v>1.404821894005213</v>
       </c>
       <c r="M22" t="n">
-        <v>992708001792</v>
+        <v>87123763200</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2079,33 +2075,33 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1379328934242756</v>
+        <v>0.2012630532883566</v>
       </c>
       <c r="S22" t="n">
-        <v>1.481635619683764</v>
+        <v>0.01123274714484013</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Hewlett Packard Enterprise Comp</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64.3</v>
+        <v>63.1</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2113,28 +2109,26 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.7634291720222148</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.4181552919037022</v>
-      </c>
+        <v>0.06370170685761956</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.108219996</v>
+        <v>0.36622003</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07877000000000001</v>
+        <v>0.02641</v>
       </c>
       <c r="J23" t="n">
-        <v>0.009835622984111891</v>
+        <v>0.3013310357337202</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5345836817584517</v>
+        <v>-0.6401233448213315</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01839865921787724</v>
+        <v>0.4707390195522809</v>
       </c>
       <c r="M23" t="n">
-        <v>27497285632</v>
+        <v>73183133696</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2143,43 +2137,43 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
+          <t>Positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5133767476961146</v>
+        <v>0.2403375620276105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6571654881653397</v>
+        <v>1.096488070348117</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Everpure, Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.5</v>
+        <v>62.7</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2187,37 +2181,37 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.0998020993811779</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3372469555379434</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H24" t="n">
-        <v>0.69734</v>
+        <v>0.60081</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03031</v>
+        <v>0.12174</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.04405333678555245</v>
+        <v>0.07698409354261027</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6324681209139751</v>
+        <v>-0.3445345693317884</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.06965305495855079</v>
+        <v>0.2234437423562982</v>
       </c>
       <c r="M24" t="n">
-        <v>51480281088</v>
+        <v>54923522048</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2227,30 +2221,30 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.050026595566973</v>
+        <v>0.1679105649736676</v>
       </c>
       <c r="S24" t="n">
-        <v>1.53511665531042</v>
+        <v>0.07381327913176228</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>United Rentals, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="D25" t="n">
         <v>62</v>
@@ -2261,28 +2255,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.142358869424539</v>
+        <v>0.1140989591195885</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1945038186480894</v>
+        <v>0.09200602525921697</v>
       </c>
       <c r="H25" t="n">
-        <v>0.60081</v>
+        <v>0.3848</v>
       </c>
       <c r="I25" t="n">
-        <v>0.12174</v>
+        <v>0.08767999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1253540020867492</v>
+        <v>0.224792354609378</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3044045312267105</v>
+        <v>-0.3186065032438522</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4118007100012241</v>
+        <v>0.7055485444292027</v>
       </c>
       <c r="M25" t="n">
-        <v>51753906176</v>
+        <v>64087355392</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2291,7 +2285,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2301,33 +2295,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1058625572510443</v>
+        <v>0.0184719451179236</v>
       </c>
       <c r="S25" t="n">
-        <v>0.05333975777768529</v>
+        <v>0.2981813049700142</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2335,37 +2329,37 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.06564722266304868</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4161701082120004</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H26" t="n">
-        <v>0.63802</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09882000000000001</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0229995208433158</v>
+        <v>0.1529611844737895</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3139434595112601</v>
+        <v>-0.3676470588235293</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07326007326007339</v>
+        <v>0.4160544217687075</v>
       </c>
       <c r="M26" t="n">
-        <v>13215687680</v>
+        <v>26253334528</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2375,33 +2369,33 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.148470149385324</v>
+        <v>0.08275562624462141</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3160549535784689</v>
+        <v>0.1948361786857744</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2409,28 +2403,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.09890131082105791</v>
+        <v>0.08634515122371456</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1098987103332316</v>
+        <v>0.1715090983184706</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.52112</v>
       </c>
       <c r="I27" t="n">
-        <v>0.058530003</v>
+        <v>0.1125</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1605712760277629</v>
+        <v>0.1376640397279498</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1825947677522691</v>
+        <v>-0.2240958652704307</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8793859649122802</v>
+        <v>0.6143087002601405</v>
       </c>
       <c r="M27" t="n">
-        <v>52348227584</v>
+        <v>76648448000</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2439,7 +2433,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2449,33 +2443,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.05331909101931886</v>
+        <v>0.1313687158209438</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1340021617826392</v>
+        <v>0.05380433005182961</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VeriSign, Inc.</t>
+          <t>Merck &amp; Company, Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.2</v>
+        <v>60.8</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2483,37 +2477,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.05150438997980311</v>
+        <v>0.03122213027882159</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1218387563505456</v>
+        <v>0.08433903046142621</v>
       </c>
       <c r="H28" t="n">
-        <v>0.88465</v>
+        <v>0.759</v>
       </c>
       <c r="I28" t="n">
-        <v>0.45124</v>
+        <v>0.11868</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06801870020412193</v>
+        <v>0.08557725248372727</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3123724237834991</v>
+        <v>-0.438095238095238</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2177487352445193</v>
+        <v>0.1953393806693775</v>
       </c>
       <c r="M28" t="n">
-        <v>27458095104</v>
+        <v>360083685376</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2523,33 +2517,33 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1269713176320513</v>
+        <v>0.1801567890781277</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1757718247421718</v>
+        <v>0.2418515404445902</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DoorDash, Inc.</t>
+          <t>NetApp, Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.1</v>
+        <v>60.6</v>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2557,143 +2551,147 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.2772574009717286</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>0.02866833411195269</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.03125259370681754</v>
+      </c>
       <c r="H29" t="n">
-        <v>0.52225</v>
+        <v>0.70625997</v>
       </c>
       <c r="I29" t="n">
-        <v>0.029719999</v>
+        <v>0.116560005</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3091433587786259</v>
+        <v>0.03870215897939144</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2707379134860051</v>
+        <v>-0.5402845927379785</v>
       </c>
       <c r="L29" t="n">
-        <v>1.14185469924812</v>
+        <v>0.07163291254200323</v>
       </c>
       <c r="M29" t="n">
-        <v>85143044096</v>
+        <v>40030195712</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.03655637710626336</v>
+        <v>0.2674342181428528</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2878489817923586</v>
+        <v>0.9600125499624836</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.0724890868669692</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.218985260923747</v>
+      </c>
       <c r="H30" t="n">
-        <v>0.75185996</v>
+        <v>0.31780002</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0078100003</v>
+        <v>0.09295</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1267815590459571</v>
+        <v>0.2185197875621037</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.6884816753926701</v>
+        <v>-0.2357375364056878</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.1841465990705537</v>
+        <v>0.926962209302325</v>
       </c>
       <c r="M30" t="n">
-        <v>281623035904</v>
+        <v>19769925632</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4636794379477818</v>
+        <v>0.1744336555006865</v>
       </c>
       <c r="S30" t="n">
-        <v>1.902643834280737</v>
+        <v>0.0887701830519525</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ResMed Inc.</t>
+          <t>IQVIA Holdings, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>58.6</v>
+        <v>59.8</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2701,37 +2699,37 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.1021250802553491</v>
+        <v>0.04214942539507627</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1426549686403549</v>
+        <v>0.1108105895361036</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6161799999999999</v>
+        <v>0.32968</v>
       </c>
       <c r="I31" t="n">
-        <v>0.14002</v>
+        <v>0.05061</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08768941534449026</v>
+        <v>0.1206641438741103</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.2163877417952619</v>
+        <v>-0.4211315099288122</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4052420650863798</v>
+        <v>0.2865236654804274</v>
       </c>
       <c r="M31" t="n">
-        <v>32354060288</v>
+        <v>43931738112</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2741,14 +2739,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1622679144421717</v>
+        <v>0.3089749969879045</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01103791855664848</v>
+        <v>0.5125239926419538</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-10-11 13:53:24</t>
+          <t>2026-10-18 12:00:14</t>
         </is>
       </c>
     </row>

--- a/data/compounder_radar.xlsx
+++ b/data/compounder_radar.xlsx
@@ -424,19 +424,19 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -577,16 +577,16 @@
         <v>0.05704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1868532197756543</v>
+        <v>0.1511385927505331</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3921063564603241</v>
+        <v>-0.4113529388099931</v>
       </c>
       <c r="L2" t="n">
-        <v>0.476537084127993</v>
+        <v>0.3674182885085576</v>
       </c>
       <c r="M2" t="n">
-        <v>198096093184</v>
+        <v>204573114368</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.387441522269363</v>
+        <v>0.434373830574259</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3272525767371199</v>
+        <v>0.4012684656265979</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>79</v>
@@ -651,16 +651,16 @@
         <v>0.14088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1326671392117948</v>
+        <v>0.14721950010486</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3399489651261696</v>
+        <v>-0.3342357629025186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3902560467055883</v>
+        <v>0.4404660316011642</v>
       </c>
       <c r="M3" t="n">
-        <v>3928485003264</v>
+        <v>3894773022720</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -679,14 +679,14 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3175716912141924</v>
+        <v>0.3505458714990768</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2564013495513537</v>
+        <v>0.2402514398038937</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="D4" t="n">
         <v>79</v>
@@ -725,16 +725,16 @@
         <v>0.03031</v>
       </c>
       <c r="J4" t="n">
-        <v>0.218492540924119</v>
+        <v>0.2252108975918268</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5421336988952503</v>
+        <v>-0.5396091786264494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4030233526699389</v>
+        <v>0.4173592787377911</v>
       </c>
       <c r="M4" t="n">
-        <v>41323511808</v>
+        <v>41096921088</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -753,33 +753,33 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.773344796153991</v>
+        <v>0.6619054487612797</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8517246509754277</v>
+        <v>0.7265854865482657</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>77</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -787,26 +787,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3291712528765784</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>0.1231541137431111</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3232467390277567</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.84796</v>
+        <v>0.84501</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17292999</v>
+        <v>0.11537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1096432295866259</v>
+        <v>0.03715170278637769</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4282105036822018</v>
+        <v>-0.4401444788441693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2560498368064275</v>
+        <v>0.08440797186400933</v>
       </c>
       <c r="M5" t="n">
-        <v>447040946176</v>
+        <v>21052925952</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -815,43 +817,43 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3795327427459936</v>
+        <v>0.5477997322003896</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2707835204243567</v>
+        <v>0.4128454154607788</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -859,28 +861,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1231541137431111</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.3232467390277567</v>
-      </c>
+        <v>0.3291712528765784</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.84501</v>
+        <v>0.84796</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11537</v>
+        <v>0.17292999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04155871074722772</v>
+        <v>0.05035669631512074</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4377655715618198</v>
+        <v>-0.4593646759847522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0949337121212122</v>
+        <v>0.1096224828501882</v>
       </c>
       <c r="M6" t="n">
-        <v>20963846144</v>
+        <v>472801738752</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -889,72 +889,72 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.545942424872498</v>
+        <v>0.4958564724853392</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3809931883606477</v>
+        <v>0.3750087709513767</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Eli Lilly and Company</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.2237651786474262</v>
+        <v>0.3168737488062043</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7345580184539504</v>
+        <v>0.5171329563234539</v>
       </c>
       <c r="H7" t="n">
-        <v>0.74768996</v>
+        <v>0.83399004</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04249</v>
+        <v>0.20357001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07228104529125878</v>
+        <v>0.04561957187504895</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.427766429527365</v>
+        <v>-0.3642281657845555</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1689731598880291</v>
+        <v>0.1252499838302823</v>
       </c>
       <c r="M7" t="n">
-        <v>146777391104</v>
+        <v>1135107506176</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -973,14 +973,14 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3559694876675608</v>
+        <v>0.06492932717906497</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4687564229459595</v>
+        <v>0.4451786576145109</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
@@ -996,14 +996,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High Conviction</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1019,20 +1019,20 @@
         <v>0.103310004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1211243607624359</v>
+        <v>0.2376384398255069</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3711064621106462</v>
+        <v>-0.3057480112907365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3263870967741931</v>
+        <v>0.7772362568191359</v>
       </c>
       <c r="M8" t="n">
-        <v>32468121600</v>
+        <v>29411500032</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1047,33 +1047,33 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1367419492704247</v>
+        <v>0.06228703180792938</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3447952724464796</v>
+        <v>0.2658762843547351</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1081,28 +1081,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3168737488062043</v>
+        <v>0.2237651786474262</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5171329563234539</v>
+        <v>0.7345580184539504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83399004</v>
+        <v>0.74768996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.20357001</v>
+        <v>0.04249</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05650199279253476</v>
+        <v>-0.0152485530951183</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.368495580853281</v>
+        <v>-0.4889280322093609</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1533315342933011</v>
+        <v>-0.03118772516726718</v>
       </c>
       <c r="M9" t="n">
-        <v>1120462569472</v>
+        <v>164342710272</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1121,14 +1121,14 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0975946286709144</v>
+        <v>0.5058735353383501</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3602561525872414</v>
+        <v>0.7628924247734239</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
         <v>72</v>
@@ -1167,20 +1167,20 @@
         <v>0.24063</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08855349680930336</v>
+        <v>0.08408932007697234</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2476434193903664</v>
+        <v>-0.2550994227068635</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3575846958796604</v>
+        <v>0.3296335177269294</v>
       </c>
       <c r="M10" t="n">
-        <v>540866019328</v>
+        <v>546279751680</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1195,33 +1195,33 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1295410142455946</v>
+        <v>0.1320173263967177</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1881690844923272</v>
+        <v>0.2408359712728239</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.1364359933536843</v>
+        <v>0.1546194776009138</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4666355102918431</v>
+        <v>0.3167495145145989</v>
       </c>
       <c r="H11" t="n">
-        <v>0.55724</v>
+        <v>0.80204004</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05128</v>
+        <v>0.14166</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1870541843971631</v>
+        <v>-0.05933218512139571</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6440283687943262</v>
+        <v>-0.5913661870103895</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2904440137432826</v>
+        <v>-0.1003307027433297</v>
       </c>
       <c r="M11" t="n">
-        <v>863171182592</v>
+        <v>132061126656</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1269,33 +1269,33 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0.05000296345999278</v>
+        <v>0.1811917556478946</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8993138121987871</v>
+        <v>1.134100228936122</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Veeva Systems Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1303,26 +1303,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.2391183028460648</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>0.1402968452680178</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2194365698361114</v>
+      </c>
       <c r="H12" t="n">
-        <v>0.68041</v>
+        <v>0.74961</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15755</v>
+        <v>0.07583000500000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.155143338954469</v>
+        <v>-0.06960261887072816</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3587689713322091</v>
+        <v>-0.5416976225854384</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4324324324324329</v>
+        <v>-0.1284897994171097</v>
       </c>
       <c r="M12" t="n">
-        <v>124967903232</v>
+        <v>52303036416</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1331,40 +1333,40 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3323641602816754</v>
+        <v>0.6612156607618047</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02252696549533506</v>
+        <v>1.004840804044313</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="D13" t="n">
         <v>69</v>
@@ -1375,28 +1377,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1402968452680178</v>
+        <v>0.1364359933536843</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2194365698361114</v>
+        <v>0.4666355102918431</v>
       </c>
       <c r="H13" t="n">
-        <v>0.74961</v>
+        <v>0.55724</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07583000500000001</v>
+        <v>0.05128</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.04292740688233021</v>
+        <v>0.2337854834652373</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5229733213042917</v>
+        <v>-0.6357901662183866</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08208335900437437</v>
+        <v>0.367708555254588</v>
       </c>
       <c r="M13" t="n">
-        <v>50250027008</v>
+        <v>843646697472</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1415,33 +1417,33 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5721593617047918</v>
+        <v>0.04412559911439518</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8479308781839834</v>
+        <v>0.4858399173539651</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1449,71 +1451,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.1539697807235301</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>0.1092124213025429</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1337066930484769</v>
+      </c>
       <c r="H14" t="n">
-        <v>0.75795</v>
+        <v>0.97725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04513</v>
+        <v>0.1911</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08964624495571516</v>
+        <v>0.0428236909197881</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4216236046328808</v>
+        <v>-0.2795401059031183</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2126215040397764</v>
+        <v>0.1531933701657455</v>
       </c>
       <c r="M14" t="n">
-        <v>45985210368</v>
+        <v>765810769920</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.296087460782881</v>
+        <v>0.1272938188997461</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5409028081815104</v>
+        <v>0.3235248016775754</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1521,28 +1525,26 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.06713489726936261</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.006929629272242499</v>
-      </c>
+        <v>0.1144958764235571</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.80716</v>
+        <v>0.52216</v>
       </c>
       <c r="I15" t="n">
-        <v>0.44557</v>
+        <v>0.04125</v>
       </c>
       <c r="J15" t="n">
-        <v>0.775710254426289</v>
+        <v>0.4941819614021268</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7810750534795867</v>
+        <v>-0.6906481116800141</v>
       </c>
       <c r="L15" t="n">
-        <v>0.993131519142241</v>
+        <v>0.7155336459257381</v>
       </c>
       <c r="M15" t="n">
-        <v>994340044800</v>
+        <v>205362987008</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1551,43 +1553,43 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01561978706208844</v>
+        <v>0.2082249909780256</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9318203848570095</v>
+        <v>0.39137179576396</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1595,26 +1597,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1144958764235571</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>0.08087962506974211</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6534957812135467</v>
+      </c>
       <c r="H16" t="n">
-        <v>0.52216</v>
+        <v>0.90433</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04125</v>
+        <v>0.061079998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4895203441162268</v>
+        <v>0.1589317670668837</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6897247948031426</v>
+        <v>-0.3587073111657035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7097328496881758</v>
+        <v>0.4430681007041581</v>
       </c>
       <c r="M16" t="n">
-        <v>204751880192</v>
+        <v>34686791680</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1623,43 +1627,43 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1689739530034025</v>
+        <v>0.03971928628839638</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6317273205837473</v>
+        <v>0.1535203040672448</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68.5</v>
+        <v>64.2</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1667,28 +1671,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.03534983888485344</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.388859258627138</v>
-      </c>
+        <v>0.1539697807235301</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.19910999</v>
+        <v>0.75795</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08643000000000001</v>
+        <v>0.04513</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3127891788979655</v>
+        <v>-0.003508595647411794</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7559938898851033</v>
+        <v>-0.4744511643411591</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4137456440891388</v>
+        <v>-0.007395061728395089</v>
       </c>
       <c r="M17" t="n">
-        <v>287202967552</v>
+        <v>50607591424</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1697,43 +1699,43 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1848130923411886</v>
+        <v>0.4232751460542521</v>
       </c>
       <c r="S17" t="n">
-        <v>1.309114152270682</v>
+        <v>0.7534235282852981</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.7</v>
+        <v>63.2</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1741,28 +1743,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.1546194776009138</v>
+        <v>0.097332408585459</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3167495145145989</v>
+        <v>0.06564477917470324</v>
       </c>
       <c r="H18" t="n">
-        <v>0.80204004</v>
+        <v>0.8053900000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14166</v>
+        <v>0.06315999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.007240525039910128</v>
+        <v>0.1269973559222446</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5651274167799918</v>
+        <v>-0.3809920188023307</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.01281219920485457</v>
+        <v>0.3333333761727286</v>
       </c>
       <c r="M18" t="n">
-        <v>124092997632</v>
+        <v>26819319808</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1771,7 +1773,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1781,33 +1783,33 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.05468947517511302</v>
+        <v>0.07571567945796676</v>
       </c>
       <c r="S18" t="n">
-        <v>1.06659350502082</v>
+        <v>0.3053593259234588</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1815,32 +1817,32 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1092124213025429</v>
+        <v>0.142358869424539</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1337066930484769</v>
+        <v>0.1945038186480894</v>
       </c>
       <c r="H19" t="n">
-        <v>0.97725</v>
+        <v>0.60081</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1911</v>
+        <v>0.12174</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05006589503489711</v>
+        <v>0.04416933342411644</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2700380020367106</v>
+        <v>-0.3645060257370464</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1854031456953635</v>
+        <v>0.1211758662557202</v>
       </c>
       <c r="M19" t="n">
-        <v>755841957888</v>
+        <v>56649580544</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1855,33 +1857,33 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1186674681421549</v>
+        <v>0.2161400023766178</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2749799780563169</v>
+        <v>0.1418465503625512</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>64.90000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1889,37 +1891,37 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.08087962506974211</v>
+        <v>0.0724890868669692</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6534957812135467</v>
+        <v>0.218985260923747</v>
       </c>
       <c r="H20" t="n">
-        <v>0.90433</v>
+        <v>0.31780002</v>
       </c>
       <c r="I20" t="n">
-        <v>0.061079998</v>
+        <v>0.09295</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1633253157985812</v>
+        <v>0.1642023134002619</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3585741477764318</v>
+        <v>-0.2698057616761239</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4554854743750609</v>
+        <v>0.6085945399393329</v>
       </c>
       <c r="M20" t="n">
-        <v>34679590912</v>
+        <v>20692318208</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1929,33 +1931,33 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.09161981300347244</v>
+        <v>0.2070222397118446</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09081003438218738</v>
+        <v>0.1972557120750362</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>64.59999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1963,26 +1965,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.2900686653697968</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0.7634291720222148</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.4181552919037022</v>
+      </c>
       <c r="H21" t="n">
-        <v>0.75185996</v>
+        <v>0.108219996</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0078100003</v>
+        <v>0.07877000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08250142926250059</v>
+        <v>0.3134993928354584</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6232024275473855</v>
+        <v>-0.4086217364905889</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1323830357772917</v>
+        <v>0.7672117384843983</v>
       </c>
       <c r="M21" t="n">
-        <v>232832548864</v>
+        <v>21307996160</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1991,43 +1995,43 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
+          <t>Stærk omsætningsvækst, stærk eps-vækst, positivt momentum</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1455992397434827</v>
+        <v>0.1049982964388374</v>
       </c>
       <c r="S21" t="n">
-        <v>1.145441611909709</v>
+        <v>0.1327372322259277</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63.5</v>
+        <v>62.4</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2035,32 +2039,30 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1518674545518492</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.08526334391298396</v>
-      </c>
+        <v>0.2900686653697968</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.82921</v>
+        <v>0.75185996</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01353</v>
+        <v>-0.0078100003</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2845302773684095</v>
+        <v>-0.04006677796327207</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.202538327871016</v>
+        <v>-0.6673525643514384</v>
       </c>
       <c r="L22" t="n">
-        <v>1.404821894005213</v>
+        <v>-0.06003839664901965</v>
       </c>
       <c r="M22" t="n">
-        <v>87123763200</v>
+        <v>263734902784</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2069,39 +2071,39 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2012630532883566</v>
+        <v>0.4300705482836764</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01123274714484013</v>
+        <v>1.299065043784106</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Comp</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.1</v>
+        <v>62.3</v>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2109,26 +2111,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.06370170685761956</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>0.03534983888485344</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.388859258627138</v>
+      </c>
       <c r="H23" t="n">
-        <v>0.36622003</v>
+        <v>0.19910999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02641</v>
+        <v>0.08643000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3013310357337202</v>
+        <v>0.2991849969327842</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6401233448213315</v>
+        <v>-0.7585224783104022</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4707390195522809</v>
+        <v>0.3944312864652534</v>
       </c>
       <c r="M23" t="n">
-        <v>73183133696</v>
+        <v>290210381824</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2137,43 +2141,43 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>88.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2403375620276105</v>
+        <v>0.070652520938985</v>
       </c>
       <c r="S23" t="n">
-        <v>1.096488070348117</v>
+        <v>1.118689377170916</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>62.7</v>
+        <v>62.1</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2181,70 +2185,68 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.142358869424539</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1945038186480894</v>
-      </c>
+        <v>0.2694953937625746</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.60081</v>
+        <v>0.79536</v>
       </c>
       <c r="I24" t="n">
-        <v>0.12174</v>
+        <v>0.0018000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07698409354261027</v>
+        <v>0.0865794548488783</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3445345693317884</v>
+        <v>-0.6365288336732802</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2234437423562982</v>
+        <v>0.1360181193195061</v>
       </c>
       <c r="M24" t="n">
-        <v>54923522048</v>
+        <v>96824573952</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, stærk eps-vækst, høj bruttomargin</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1679105649736676</v>
+        <v>0.07063445264440937</v>
       </c>
       <c r="S24" t="n">
-        <v>0.07381327913176228</v>
+        <v>1.082561034863647</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>United Rentals, Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>61.5</v>
+        <v>61.8</v>
       </c>
       <c r="D25" t="n">
         <v>62</v>
@@ -2255,28 +2257,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1140989591195885</v>
+        <v>0.05150438997980311</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09200602525921697</v>
+        <v>0.1218387563505456</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3848</v>
+        <v>0.88567</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08767999999999999</v>
+        <v>0.54899</v>
       </c>
       <c r="J25" t="n">
-        <v>0.224792354609378</v>
+        <v>0.1201385189131592</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3186065032438522</v>
+        <v>-0.3045418220564731</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7055485444292027</v>
+        <v>0.3944893942707191</v>
       </c>
       <c r="M25" t="n">
-        <v>64087355392</v>
+        <v>26938703872</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2285,7 +2287,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Stærk omsætningsvækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2295,33 +2297,33 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0184719451179236</v>
+        <v>0.09599592112390942</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2981813049700142</v>
+        <v>0.1218530523055652</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>Merck &amp; Company, Inc.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>61.5</v>
+        <v>61.1</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2329,28 +2331,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.097332408585459</v>
+        <v>0.03122213027882159</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06564477917470324</v>
+        <v>0.08433903046142621</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8053900000000001</v>
+        <v>0.759</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06315999999999999</v>
+        <v>0.11868</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1529611844737895</v>
+        <v>0.09974530185172426</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3676470588235293</v>
+        <v>-0.4354649962139464</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4160544217687075</v>
+        <v>0.2290546949098954</v>
       </c>
       <c r="M26" t="n">
-        <v>26253334528</v>
+        <v>358406029312</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2369,30 +2371,30 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.08275562624462141</v>
+        <v>0.1175245328199832</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1948361786857744</v>
+        <v>0.3152666583452968</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60.9</v>
+        <v>61</v>
       </c>
       <c r="D27" t="n">
         <v>61</v>
@@ -2403,37 +2405,37 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.08634515122371456</v>
+        <v>0.09890131082105791</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1715090983184706</v>
+        <v>0.1098987103332316</v>
       </c>
       <c r="H27" t="n">
-        <v>0.52112</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1125</v>
+        <v>0.060949996</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1376640397279498</v>
+        <v>0.1139820592823713</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2240958652704307</v>
+        <v>-0.2536076443057723</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6143087002601405</v>
+        <v>0.4494425221068817</v>
       </c>
       <c r="M27" t="n">
-        <v>76648448000</v>
+        <v>57328713728</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
+          <t>Høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2443,33 +2445,33 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1313687158209438</v>
+        <v>0.09545147142315002</v>
       </c>
       <c r="S27" t="n">
-        <v>0.05380433005182961</v>
+        <v>0.1487854628997956</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Merck &amp; Company, Inc.</t>
+          <t>Hewlett Packard Enterprise Comp</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2477,28 +2479,26 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.03122213027882159</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.08433903046142621</v>
-      </c>
+        <v>0.06370170685761956</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.759</v>
+        <v>0.36622003</v>
       </c>
       <c r="I28" t="n">
-        <v>0.11868</v>
+        <v>0.02641</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08557725248372727</v>
+        <v>0.2655209031575234</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.438095238095238</v>
+        <v>-0.6500264596930676</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1953393806693775</v>
+        <v>0.4084770691994573</v>
       </c>
       <c r="M28" t="n">
-        <v>360083685376</v>
+        <v>75253981184</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2507,81 +2507,81 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Positivt momentum, analytiker-upside over 20 %</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1801567890781277</v>
+        <v>0.1793606413918047</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2418515404445902</v>
+        <v>1.024135811166923</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NetApp, Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.6</v>
+        <v>59.7</v>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.02866833411195269</v>
+        <v>0.0405993172034298</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03125259370681754</v>
+        <v>0.5822968332827563</v>
       </c>
       <c r="H29" t="n">
-        <v>0.70625997</v>
+        <v>0.57167</v>
       </c>
       <c r="I29" t="n">
-        <v>0.116560005</v>
+        <v>0.04658</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03870215897939144</v>
+        <v>0.1723875061005369</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.5402845927379785</v>
+        <v>-0.2776964372864812</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07163291254200323</v>
+        <v>0.6207768014059756</v>
       </c>
       <c r="M29" t="n">
-        <v>40030195712</v>
+        <v>16553660416</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Høj bruttomargin, positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2591,62 +2591,62 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.2674342181428528</v>
+        <v>0.1302100255129108</v>
       </c>
       <c r="S29" t="n">
-        <v>0.9600125499624836</v>
+        <v>0.1772302555367564</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions,</t>
+          <t>Vertex Pharmaceuticals Incorpor</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.0724890868669692</v>
+        <v>0.1035218340064799</v>
       </c>
       <c r="G30" t="n">
-        <v>0.218985260923747</v>
+        <v>0.06118290879552779</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31780002</v>
+        <v>0.54957</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09295</v>
+        <v>0.11926</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2185197875621037</v>
+        <v>0.09072643292042826</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2357375364056878</v>
+        <v>-0.2305078922756856</v>
       </c>
       <c r="L30" t="n">
-        <v>0.926962209302325</v>
+        <v>0.3935936076840275</v>
       </c>
       <c r="M30" t="n">
-        <v>19769925632</v>
+        <v>132711464960</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Stærk eps-vækst, positivt momentum, analytiker-upside over 20 %</t>
+          <t>Stærk omsætningsvækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2665,33 +2665,33 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1744336555006865</v>
+        <v>0.0937995671728209</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0887701830519525</v>
+        <v>0.2176206332271446</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>59.8</v>
+        <v>59.1</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2699,37 +2699,37 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.04214942539507627</v>
+        <v>0.02573617986261412</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1108105895361036</v>
+        <v>0.230389935777624</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32968</v>
+        <v>0.79603994</v>
       </c>
       <c r="I31" t="n">
-        <v>0.05061</v>
+        <v>0.14085001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1206641438741103</v>
+        <v>0.02661048449115611</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4211315099288122</v>
+        <v>-0.2692899256600871</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2865236654804274</v>
+        <v>0.0988172298905283</v>
       </c>
       <c r="M31" t="n">
-        <v>43931738112</v>
+        <v>193482604544</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Positivt momentum</t>
+          <t>Stærk eps-vækst, høj bruttomargin, positivt momentum</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2739,14 +2739,14 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3089749969879045</v>
+        <v>0.2022589859310977</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5125239926419538</v>
+        <v>0.2112740635348627</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:14</t>
+          <t>2026-10-25 12:25:44</t>
         </is>
       </c>
     </row>
